--- a/forecast-results/河北电网披露及电价预估数据-20261020.xlsx
+++ b/forecast-results/河北电网披露及电价预估数据-20261020.xlsx
@@ -3764,25 +3764,25 @@
         <v>1</v>
       </c>
       <c r="D2" s="21" t="n">
-        <v>14543</v>
+        <v>13801</v>
       </c>
       <c r="E2" s="22" t="n">
-        <v>14984</v>
+        <v>14944</v>
       </c>
       <c r="F2" s="21" t="n">
-        <v>14420</v>
+        <v>13621</v>
       </c>
       <c r="G2" s="21" t="n">
-        <v>14478</v>
+        <v>13654</v>
       </c>
       <c r="H2" s="22" t="n">
-        <v>14345</v>
+        <v>13956</v>
       </c>
       <c r="I2" s="21" t="n">
-        <v>13885</v>
+        <v>12936</v>
       </c>
       <c r="J2" s="22" t="n">
-        <v>15007</v>
+        <v>13388</v>
       </c>
     </row>
     <row r="3">
@@ -3796,25 +3796,25 @@
         <v>1</v>
       </c>
       <c r="D3" s="21" t="n">
-        <v>14462</v>
+        <v>13807</v>
       </c>
       <c r="E3" s="22" t="n">
-        <v>14940</v>
+        <v>14900</v>
       </c>
       <c r="F3" s="21" t="n">
-        <v>14434</v>
+        <v>13649</v>
       </c>
       <c r="G3" s="21" t="n">
-        <v>14343</v>
+        <v>13636</v>
       </c>
       <c r="H3" s="22" t="n">
-        <v>14320</v>
+        <v>13841</v>
       </c>
       <c r="I3" s="21" t="n">
-        <v>13846</v>
+        <v>13049</v>
       </c>
       <c r="J3" s="22" t="n">
-        <v>14744</v>
+        <v>13464</v>
       </c>
     </row>
     <row r="4">
@@ -3828,25 +3828,25 @@
         <v>1</v>
       </c>
       <c r="D4" s="21" t="n">
-        <v>14344</v>
+        <v>13830</v>
       </c>
       <c r="E4" s="22" t="n">
-        <v>14907</v>
+        <v>14866</v>
       </c>
       <c r="F4" s="21" t="n">
-        <v>14256</v>
+        <v>13799</v>
       </c>
       <c r="G4" s="21" t="n">
-        <v>14413</v>
+        <v>13658</v>
       </c>
       <c r="H4" s="22" t="n">
-        <v>14332</v>
+        <v>13785</v>
       </c>
       <c r="I4" s="21" t="n">
-        <v>13771</v>
+        <v>13091</v>
       </c>
       <c r="J4" s="22" t="n">
-        <v>14228</v>
+        <v>13485</v>
       </c>
     </row>
     <row r="5">
@@ -3860,25 +3860,25 @@
         <v>1</v>
       </c>
       <c r="D5" s="21" t="n">
-        <v>14160</v>
+        <v>13692</v>
       </c>
       <c r="E5" s="22" t="n">
-        <v>14851</v>
+        <v>14811</v>
       </c>
       <c r="F5" s="21" t="n">
-        <v>14255</v>
+        <v>13732</v>
       </c>
       <c r="G5" s="21" t="n">
-        <v>13559</v>
+        <v>13045</v>
       </c>
       <c r="H5" s="22" t="n">
-        <v>14378</v>
+        <v>13790</v>
       </c>
       <c r="I5" s="21" t="n">
-        <v>13720</v>
+        <v>12886</v>
       </c>
       <c r="J5" s="22" t="n">
-        <v>14048</v>
+        <v>13603</v>
       </c>
     </row>
     <row r="6">
@@ -3892,25 +3892,25 @@
         <v>2</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>14140</v>
+        <v>13661</v>
       </c>
       <c r="E6" s="22" t="n">
-        <v>14869</v>
+        <v>14829</v>
       </c>
       <c r="F6" s="21" t="n">
-        <v>14241</v>
+        <v>13708</v>
       </c>
       <c r="G6" s="21" t="n">
-        <v>13460</v>
+        <v>13016</v>
       </c>
       <c r="H6" s="22" t="n">
-        <v>14383</v>
+        <v>13770</v>
       </c>
       <c r="I6" s="21" t="n">
-        <v>13717</v>
+        <v>12854</v>
       </c>
       <c r="J6" s="22" t="n">
-        <v>14017</v>
+        <v>13490</v>
       </c>
     </row>
     <row r="7">
@@ -3924,25 +3924,25 @@
         <v>2</v>
       </c>
       <c r="D7" s="21" t="n">
-        <v>14107</v>
+        <v>13599</v>
       </c>
       <c r="E7" s="22" t="n">
-        <v>14814</v>
+        <v>14774</v>
       </c>
       <c r="F7" s="21" t="n">
-        <v>14193</v>
+        <v>13740</v>
       </c>
       <c r="G7" s="21" t="n">
-        <v>13323</v>
+        <v>13162</v>
       </c>
       <c r="H7" s="22" t="n">
-        <v>14313</v>
+        <v>13694</v>
       </c>
       <c r="I7" s="21" t="n">
-        <v>13790</v>
+        <v>12582</v>
       </c>
       <c r="J7" s="22" t="n">
-        <v>14062</v>
+        <v>13321</v>
       </c>
     </row>
     <row r="8">
@@ -3956,25 +3956,25 @@
         <v>2</v>
       </c>
       <c r="D8" s="21" t="n">
-        <v>14156</v>
+        <v>13654</v>
       </c>
       <c r="E8" s="22" t="n">
-        <v>14742</v>
+        <v>14702</v>
       </c>
       <c r="F8" s="21" t="n">
-        <v>14215</v>
+        <v>13847</v>
       </c>
       <c r="G8" s="21" t="n">
-        <v>13842</v>
+        <v>13762</v>
       </c>
       <c r="H8" s="22" t="n">
-        <v>14209</v>
+        <v>13474</v>
       </c>
       <c r="I8" s="21" t="n">
-        <v>13773</v>
+        <v>12538</v>
       </c>
       <c r="J8" s="22" t="n">
-        <v>14013</v>
+        <v>13263</v>
       </c>
     </row>
     <row r="9">
@@ -3988,25 +3988,25 @@
         <v>2</v>
       </c>
       <c r="D9" s="21" t="n">
-        <v>14244</v>
+        <v>13780</v>
       </c>
       <c r="E9" s="22" t="n">
-        <v>14822</v>
+        <v>14780</v>
       </c>
       <c r="F9" s="21" t="n">
-        <v>14382</v>
+        <v>13891</v>
       </c>
       <c r="G9" s="21" t="n">
-        <v>14127</v>
+        <v>13630</v>
       </c>
       <c r="H9" s="22" t="n">
-        <v>14310</v>
+        <v>13700</v>
       </c>
       <c r="I9" s="21" t="n">
-        <v>13782</v>
+        <v>12904</v>
       </c>
       <c r="J9" s="22" t="n">
-        <v>13888</v>
+        <v>13476</v>
       </c>
     </row>
     <row r="10">
@@ -4020,25 +4020,25 @@
         <v>3</v>
       </c>
       <c r="D10" s="21" t="n">
-        <v>15792</v>
+        <v>15459</v>
       </c>
       <c r="E10" s="22" t="n">
-        <v>16079</v>
+        <v>16033</v>
       </c>
       <c r="F10" s="21" t="n">
-        <v>15885</v>
+        <v>15438</v>
       </c>
       <c r="G10" s="21" t="n">
-        <v>15966</v>
+        <v>15505</v>
       </c>
       <c r="H10" s="22" t="n">
-        <v>15623</v>
+        <v>15150</v>
       </c>
       <c r="I10" s="21" t="n">
-        <v>15526</v>
+        <v>15348</v>
       </c>
       <c r="J10" s="22" t="n">
-        <v>15569</v>
+        <v>15084</v>
       </c>
     </row>
     <row r="11">
@@ -4052,25 +4052,25 @@
         <v>3</v>
       </c>
       <c r="D11" s="21" t="n">
-        <v>15786</v>
+        <v>15413</v>
       </c>
       <c r="E11" s="22" t="n">
-        <v>16287</v>
+        <v>16253</v>
       </c>
       <c r="F11" s="21" t="n">
-        <v>15843</v>
+        <v>15435</v>
       </c>
       <c r="G11" s="21" t="n">
-        <v>15981</v>
+        <v>15257</v>
       </c>
       <c r="H11" s="22" t="n">
-        <v>15513</v>
+        <v>15080</v>
       </c>
       <c r="I11" s="21" t="n">
-        <v>15400</v>
+        <v>15121</v>
       </c>
       <c r="J11" s="22" t="n">
-        <v>15524</v>
+        <v>15065</v>
       </c>
     </row>
     <row r="12">
@@ -4084,25 +4084,25 @@
         <v>3</v>
       </c>
       <c r="D12" s="21" t="n">
-        <v>15698</v>
+        <v>15272</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>16177</v>
+        <v>16143</v>
       </c>
       <c r="F12" s="21" t="n">
-        <v>15721</v>
+        <v>15283</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>15874</v>
+        <v>15315</v>
       </c>
       <c r="H12" s="22" t="n">
-        <v>15446</v>
+        <v>14943</v>
       </c>
       <c r="I12" s="21" t="n">
-        <v>15306</v>
+        <v>14864</v>
       </c>
       <c r="J12" s="22" t="n">
-        <v>15502</v>
+        <v>14795</v>
       </c>
     </row>
     <row r="13">
@@ -4116,25 +4116,25 @@
         <v>3</v>
       </c>
       <c r="D13" s="21" t="n">
-        <v>15660</v>
+        <v>15215</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>16109</v>
+        <v>16074</v>
       </c>
       <c r="F13" s="21" t="n">
-        <v>15653</v>
+        <v>15106</v>
       </c>
       <c r="G13" s="21" t="n">
-        <v>15874</v>
+        <v>15315</v>
       </c>
       <c r="H13" s="22" t="n">
-        <v>15322</v>
+        <v>14853</v>
       </c>
       <c r="I13" s="21" t="n">
-        <v>15353</v>
+        <v>14844</v>
       </c>
       <c r="J13" s="22" t="n">
-        <v>15488</v>
+        <v>14813</v>
       </c>
     </row>
     <row r="14">
@@ -4148,25 +4148,25 @@
         <v>4</v>
       </c>
       <c r="D14" s="21" t="n">
-        <v>15646</v>
+        <v>15241</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>16142</v>
+        <v>16107</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>15509</v>
+        <v>15234</v>
       </c>
       <c r="G14" s="21" t="n">
-        <v>15873</v>
+        <v>15315</v>
       </c>
       <c r="H14" s="22" t="n">
-        <v>15346</v>
+        <v>14884</v>
       </c>
       <c r="I14" s="21" t="n">
-        <v>15334</v>
+        <v>14799</v>
       </c>
       <c r="J14" s="22" t="n">
-        <v>15508</v>
+        <v>14819</v>
       </c>
     </row>
     <row r="15">
@@ -4180,25 +4180,25 @@
         <v>4</v>
       </c>
       <c r="D15" s="21" t="n">
-        <v>15609</v>
+        <v>15182</v>
       </c>
       <c r="E15" s="22" t="n">
-        <v>16059</v>
+        <v>16026</v>
       </c>
       <c r="F15" s="21" t="n">
-        <v>15357</v>
+        <v>14955</v>
       </c>
       <c r="G15" s="21" t="n">
-        <v>15873</v>
+        <v>15499</v>
       </c>
       <c r="H15" s="22" t="n">
-        <v>15413</v>
+        <v>14866</v>
       </c>
       <c r="I15" s="21" t="n">
-        <v>15235</v>
+        <v>14708</v>
       </c>
       <c r="J15" s="22" t="n">
-        <v>15572</v>
+        <v>14755</v>
       </c>
     </row>
     <row r="16">
@@ -4212,25 +4212,25 @@
         <v>4</v>
       </c>
       <c r="D16" s="21" t="n">
-        <v>15566</v>
+        <v>15127</v>
       </c>
       <c r="E16" s="22" t="n">
-        <v>16026</v>
+        <v>15991</v>
       </c>
       <c r="F16" s="21" t="n">
-        <v>15336</v>
+        <v>14895</v>
       </c>
       <c r="G16" s="21" t="n">
-        <v>15988</v>
+        <v>15521</v>
       </c>
       <c r="H16" s="22" t="n">
-        <v>15299</v>
+        <v>14810</v>
       </c>
       <c r="I16" s="21" t="n">
-        <v>15125</v>
+        <v>14585</v>
       </c>
       <c r="J16" s="22" t="n">
-        <v>15462</v>
+        <v>14664</v>
       </c>
     </row>
     <row r="17">
@@ -4244,25 +4244,25 @@
         <v>4</v>
       </c>
       <c r="D17" s="21" t="n">
-        <v>15624</v>
+        <v>15208</v>
       </c>
       <c r="E17" s="22" t="n">
-        <v>16028</v>
+        <v>15993</v>
       </c>
       <c r="F17" s="21" t="n">
-        <v>15408</v>
+        <v>15023</v>
       </c>
       <c r="G17" s="21" t="n">
-        <v>16009</v>
+        <v>15547</v>
       </c>
       <c r="H17" s="22" t="n">
-        <v>15340</v>
+        <v>14835</v>
       </c>
       <c r="I17" s="21" t="n">
-        <v>15255</v>
+        <v>14735</v>
       </c>
       <c r="J17" s="22" t="n">
-        <v>15561</v>
+        <v>14842</v>
       </c>
     </row>
     <row r="18">
@@ -4276,25 +4276,25 @@
         <v>5</v>
       </c>
       <c r="D18" s="21" t="n">
-        <v>15780</v>
+        <v>15336</v>
       </c>
       <c r="E18" s="22" t="n">
-        <v>16107</v>
+        <v>16072</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>15789</v>
+        <v>15302</v>
       </c>
       <c r="G18" s="21" t="n">
-        <v>16009</v>
+        <v>15547</v>
       </c>
       <c r="H18" s="22" t="n">
-        <v>15375</v>
+        <v>14898</v>
       </c>
       <c r="I18" s="21" t="n">
-        <v>15521</v>
+        <v>14905</v>
       </c>
       <c r="J18" s="22" t="n">
-        <v>15745</v>
+        <v>15027</v>
       </c>
     </row>
     <row r="19">
@@ -4308,25 +4308,25 @@
         <v>5</v>
       </c>
       <c r="D19" s="21" t="n">
-        <v>15876</v>
+        <v>15488</v>
       </c>
       <c r="E19" s="22" t="n">
-        <v>16146</v>
+        <v>16111</v>
       </c>
       <c r="F19" s="21" t="n">
-        <v>15944</v>
+        <v>15585</v>
       </c>
       <c r="G19" s="21" t="n">
-        <v>16009</v>
+        <v>15573</v>
       </c>
       <c r="H19" s="22" t="n">
-        <v>15486</v>
+        <v>15019</v>
       </c>
       <c r="I19" s="21" t="n">
-        <v>15772</v>
+        <v>15219</v>
       </c>
       <c r="J19" s="22" t="n">
-        <v>15787</v>
+        <v>15182</v>
       </c>
     </row>
     <row r="20">
@@ -4340,25 +4340,25 @@
         <v>5</v>
       </c>
       <c r="D20" s="21" t="n">
-        <v>15966</v>
+        <v>15561</v>
       </c>
       <c r="E20" s="22" t="n">
-        <v>16163</v>
+        <v>16128</v>
       </c>
       <c r="F20" s="21" t="n">
-        <v>16160</v>
+        <v>15728</v>
       </c>
       <c r="G20" s="21" t="n">
-        <v>16063</v>
+        <v>15606</v>
       </c>
       <c r="H20" s="22" t="n">
-        <v>15512</v>
+        <v>15000</v>
       </c>
       <c r="I20" s="21" t="n">
-        <v>15881</v>
+        <v>15383</v>
       </c>
       <c r="J20" s="22" t="n">
-        <v>15914</v>
+        <v>15290</v>
       </c>
     </row>
     <row r="21">
@@ -4372,25 +4372,25 @@
         <v>5</v>
       </c>
       <c r="D21" s="21" t="n">
-        <v>16043</v>
+        <v>15646</v>
       </c>
       <c r="E21" s="22" t="n">
-        <v>16215</v>
+        <v>16180</v>
       </c>
       <c r="F21" s="21" t="n">
-        <v>16320</v>
+        <v>15788</v>
       </c>
       <c r="G21" s="21" t="n">
-        <v>16113</v>
+        <v>15594</v>
       </c>
       <c r="H21" s="22" t="n">
-        <v>15630</v>
+        <v>15172</v>
       </c>
       <c r="I21" s="21" t="n">
-        <v>15969</v>
+        <v>15517</v>
       </c>
       <c r="J21" s="22" t="n">
-        <v>15916</v>
+        <v>15420</v>
       </c>
     </row>
     <row r="22">
@@ -4404,25 +4404,25 @@
         <v>6</v>
       </c>
       <c r="D22" s="21" t="n">
-        <v>16137</v>
+        <v>15768</v>
       </c>
       <c r="E22" s="22" t="n">
-        <v>16367</v>
+        <v>16333</v>
       </c>
       <c r="F22" s="21" t="n">
-        <v>16444</v>
+        <v>15960</v>
       </c>
       <c r="G22" s="21" t="n">
-        <v>16152</v>
+        <v>15647</v>
       </c>
       <c r="H22" s="22" t="n">
-        <v>15698</v>
+        <v>15334</v>
       </c>
       <c r="I22" s="21" t="n">
-        <v>16047</v>
+        <v>15697</v>
       </c>
       <c r="J22" s="22" t="n">
-        <v>16003</v>
+        <v>15433</v>
       </c>
     </row>
     <row r="23">
@@ -4436,25 +4436,25 @@
         <v>6</v>
       </c>
       <c r="D23" s="21" t="n">
-        <v>16281</v>
+        <v>15921</v>
       </c>
       <c r="E23" s="22" t="n">
-        <v>16443</v>
+        <v>16410</v>
       </c>
       <c r="F23" s="21" t="n">
-        <v>16616</v>
+        <v>16052</v>
       </c>
       <c r="G23" s="21" t="n">
-        <v>16150</v>
+        <v>15703</v>
       </c>
       <c r="H23" s="22" t="n">
-        <v>15913</v>
+        <v>15551</v>
       </c>
       <c r="I23" s="21" t="n">
-        <v>16312</v>
+        <v>15985</v>
       </c>
       <c r="J23" s="22" t="n">
-        <v>16174</v>
+        <v>15653</v>
       </c>
     </row>
     <row r="24">
@@ -4468,25 +4468,25 @@
         <v>6</v>
       </c>
       <c r="D24" s="21" t="n">
-        <v>16442</v>
+        <v>16014</v>
       </c>
       <c r="E24" s="22" t="n">
-        <v>16562</v>
+        <v>16528</v>
       </c>
       <c r="F24" s="21" t="n">
-        <v>16999</v>
+        <v>16260</v>
       </c>
       <c r="G24" s="21" t="n">
-        <v>16365</v>
+        <v>15669</v>
       </c>
       <c r="H24" s="22" t="n">
-        <v>16157</v>
+        <v>15772</v>
       </c>
       <c r="I24" s="21" t="n">
-        <v>16357</v>
+        <v>16083</v>
       </c>
       <c r="J24" s="22" t="n">
-        <v>16143</v>
+        <v>15611</v>
       </c>
     </row>
     <row r="25">
@@ -4500,25 +4500,25 @@
         <v>6</v>
       </c>
       <c r="D25" s="21" t="n">
-        <v>16690</v>
+        <v>16359</v>
       </c>
       <c r="E25" s="22" t="n">
-        <v>16722</v>
+        <v>16688</v>
       </c>
       <c r="F25" s="21" t="n">
-        <v>17369</v>
+        <v>16953</v>
       </c>
       <c r="G25" s="21" t="n">
-        <v>16585</v>
+        <v>16213</v>
       </c>
       <c r="H25" s="22" t="n">
-        <v>16487</v>
+        <v>16094</v>
       </c>
       <c r="I25" s="21" t="n">
-        <v>16513</v>
+        <v>16225</v>
       </c>
       <c r="J25" s="22" t="n">
-        <v>16419</v>
+        <v>15845</v>
       </c>
     </row>
     <row r="26">
@@ -4532,25 +4532,25 @@
         <v>7</v>
       </c>
       <c r="D26" s="21" t="n">
-        <v>16893</v>
+        <v>16646</v>
       </c>
       <c r="E26" s="22" t="n">
-        <v>16543</v>
+        <v>16509</v>
       </c>
       <c r="F26" s="21" t="n">
-        <v>17336</v>
+        <v>17187</v>
       </c>
       <c r="G26" s="21" t="n">
-        <v>16757</v>
+        <v>16601</v>
       </c>
       <c r="H26" s="22" t="n">
-        <v>16943</v>
+        <v>16507</v>
       </c>
       <c r="I26" s="21" t="n">
-        <v>16931</v>
+        <v>16765</v>
       </c>
       <c r="J26" s="22" t="n">
-        <v>16938</v>
+        <v>16316</v>
       </c>
     </row>
     <row r="27">
@@ -4564,25 +4564,25 @@
         <v>7</v>
       </c>
       <c r="D27" s="21" t="n">
-        <v>17496</v>
+        <v>17211</v>
       </c>
       <c r="E27" s="22" t="n">
-        <v>16861</v>
+        <v>16825</v>
       </c>
       <c r="F27" s="21" t="n">
-        <v>17929</v>
+        <v>17673</v>
       </c>
       <c r="G27" s="21" t="n">
-        <v>17502</v>
+        <v>17346</v>
       </c>
       <c r="H27" s="22" t="n">
-        <v>17750</v>
+        <v>17295</v>
       </c>
       <c r="I27" s="21" t="n">
-        <v>17536</v>
+        <v>17360</v>
       </c>
       <c r="J27" s="22" t="n">
-        <v>17577</v>
+        <v>16865</v>
       </c>
     </row>
     <row r="28">
@@ -4596,25 +4596,25 @@
         <v>7</v>
       </c>
       <c r="D28" s="21" t="n">
-        <v>18068</v>
+        <v>17772</v>
       </c>
       <c r="E28" s="22" t="n">
-        <v>17144</v>
+        <v>17110</v>
       </c>
       <c r="F28" s="21" t="n">
-        <v>18139</v>
+        <v>17855</v>
       </c>
       <c r="G28" s="21" t="n">
-        <v>18337</v>
+        <v>18096</v>
       </c>
       <c r="H28" s="22" t="n">
-        <v>18313</v>
+        <v>17897</v>
       </c>
       <c r="I28" s="21" t="n">
-        <v>18345</v>
+        <v>18186</v>
       </c>
       <c r="J28" s="22" t="n">
-        <v>18388</v>
+        <v>17676</v>
       </c>
     </row>
     <row r="29">
@@ -4628,25 +4628,25 @@
         <v>7</v>
       </c>
       <c r="D29" s="21" t="n">
-        <v>18458</v>
+        <v>18142</v>
       </c>
       <c r="E29" s="22" t="n">
-        <v>17376</v>
+        <v>17344</v>
       </c>
       <c r="F29" s="21" t="n">
-        <v>18451</v>
+        <v>18333</v>
       </c>
       <c r="G29" s="21" t="n">
-        <v>18761</v>
+        <v>18446</v>
       </c>
       <c r="H29" s="22" t="n">
-        <v>18668</v>
+        <v>18235</v>
       </c>
       <c r="I29" s="21" t="n">
-        <v>18964</v>
+        <v>18579</v>
       </c>
       <c r="J29" s="22" t="n">
-        <v>18825</v>
+        <v>18132</v>
       </c>
     </row>
     <row r="30">
@@ -4660,25 +4660,25 @@
         <v>8</v>
       </c>
       <c r="D30" s="21" t="n">
-        <v>18670</v>
+        <v>18340</v>
       </c>
       <c r="E30" s="22" t="n">
-        <v>17589</v>
+        <v>17558</v>
       </c>
       <c r="F30" s="21" t="n">
-        <v>18856</v>
+        <v>18554</v>
       </c>
       <c r="G30" s="21" t="n">
-        <v>18778</v>
+        <v>18549</v>
       </c>
       <c r="H30" s="22" t="n">
-        <v>18739</v>
+        <v>18328</v>
       </c>
       <c r="I30" s="21" t="n">
-        <v>19218</v>
+        <v>18777</v>
       </c>
       <c r="J30" s="22" t="n">
-        <v>19125</v>
+        <v>18483</v>
       </c>
     </row>
     <row r="31">
@@ -4692,25 +4692,25 @@
         <v>8</v>
       </c>
       <c r="D31" s="21" t="n">
-        <v>18376</v>
+        <v>18160</v>
       </c>
       <c r="E31" s="22" t="n">
-        <v>17494</v>
+        <v>17466</v>
       </c>
       <c r="F31" s="21" t="n">
-        <v>18649</v>
+        <v>18421</v>
       </c>
       <c r="G31" s="21" t="n">
-        <v>18175</v>
+        <v>18416</v>
       </c>
       <c r="H31" s="22" t="n">
-        <v>18616</v>
+        <v>18264</v>
       </c>
       <c r="I31" s="21" t="n">
-        <v>18876</v>
+        <v>18556</v>
       </c>
       <c r="J31" s="22" t="n">
-        <v>18706</v>
+        <v>18030</v>
       </c>
     </row>
     <row r="32">
@@ -4724,25 +4724,25 @@
         <v>8</v>
       </c>
       <c r="D32" s="21" t="n">
+        <v>17984</v>
+      </c>
+      <c r="E32" s="22" t="n">
+        <v>17286</v>
+      </c>
+      <c r="F32" s="21" t="n">
         <v>18161</v>
       </c>
-      <c r="E32" s="22" t="n">
-        <v>17314</v>
-      </c>
-      <c r="F32" s="21" t="n">
-        <v>18163</v>
-      </c>
       <c r="G32" s="21" t="n">
-        <v>17962</v>
+        <v>18114</v>
       </c>
       <c r="H32" s="22" t="n">
-        <v>18477</v>
+        <v>18149</v>
       </c>
       <c r="I32" s="21" t="n">
-        <v>18671</v>
+        <v>18434</v>
       </c>
       <c r="J32" s="22" t="n">
-        <v>18643</v>
+        <v>17968</v>
       </c>
     </row>
     <row r="33">
@@ -4756,25 +4756,25 @@
         <v>8</v>
       </c>
       <c r="D33" s="21" t="n">
-        <v>18292</v>
+        <v>18039</v>
       </c>
       <c r="E33" s="22" t="n">
-        <v>17328</v>
+        <v>17300</v>
       </c>
       <c r="F33" s="21" t="n">
-        <v>18391</v>
+        <v>18210</v>
       </c>
       <c r="G33" s="21" t="n">
-        <v>18205</v>
+        <v>18252</v>
       </c>
       <c r="H33" s="22" t="n">
-        <v>18632</v>
+        <v>18215</v>
       </c>
       <c r="I33" s="21" t="n">
-        <v>18688</v>
+        <v>18514</v>
       </c>
       <c r="J33" s="22" t="n">
-        <v>18795</v>
+        <v>17963</v>
       </c>
     </row>
     <row r="34">
@@ -4788,25 +4788,25 @@
         <v>9</v>
       </c>
       <c r="D34" s="21" t="n">
-        <v>18601</v>
+        <v>18239</v>
       </c>
       <c r="E34" s="22" t="n">
-        <v>17461</v>
+        <v>17434</v>
       </c>
       <c r="F34" s="21" t="n">
-        <v>18664</v>
+        <v>18241</v>
       </c>
       <c r="G34" s="21" t="n">
-        <v>18556</v>
+        <v>18503</v>
       </c>
       <c r="H34" s="22" t="n">
-        <v>18814</v>
+        <v>18384</v>
       </c>
       <c r="I34" s="21" t="n">
-        <v>19133</v>
+        <v>18755</v>
       </c>
       <c r="J34" s="22" t="n">
-        <v>19300</v>
+        <v>18354</v>
       </c>
     </row>
     <row r="35">
@@ -4820,25 +4820,25 @@
         <v>9</v>
       </c>
       <c r="D35" s="21" t="n">
-        <v>18455</v>
+        <v>18022</v>
       </c>
       <c r="E35" s="22" t="n">
-        <v>17354</v>
+        <v>17329</v>
       </c>
       <c r="F35" s="21" t="n">
-        <v>18721</v>
+        <v>17804</v>
       </c>
       <c r="G35" s="21" t="n">
-        <v>18268</v>
+        <v>18358</v>
       </c>
       <c r="H35" s="22" t="n">
-        <v>18659</v>
+        <v>18102</v>
       </c>
       <c r="I35" s="21" t="n">
-        <v>18951</v>
+        <v>18518</v>
       </c>
       <c r="J35" s="22" t="n">
-        <v>19085</v>
+        <v>18224</v>
       </c>
     </row>
     <row r="36">
@@ -4852,25 +4852,25 @@
         <v>9</v>
       </c>
       <c r="D36" s="21" t="n">
-        <v>18171</v>
+        <v>17737</v>
       </c>
       <c r="E36" s="22" t="n">
-        <v>17116</v>
+        <v>17093</v>
       </c>
       <c r="F36" s="21" t="n">
-        <v>18301</v>
+        <v>17672</v>
       </c>
       <c r="G36" s="21" t="n">
-        <v>18192</v>
+        <v>17988</v>
       </c>
       <c r="H36" s="22" t="n">
-        <v>18287</v>
+        <v>17802</v>
       </c>
       <c r="I36" s="21" t="n">
-        <v>18530</v>
+        <v>18075</v>
       </c>
       <c r="J36" s="22" t="n">
-        <v>18882</v>
+        <v>17973</v>
       </c>
     </row>
     <row r="37">
@@ -4884,25 +4884,25 @@
         <v>9</v>
       </c>
       <c r="D37" s="21" t="n">
-        <v>17782</v>
+        <v>17365</v>
       </c>
       <c r="E37" s="22" t="n">
-        <v>16843</v>
+        <v>16821</v>
       </c>
       <c r="F37" s="21" t="n">
-        <v>17715</v>
+        <v>17101</v>
       </c>
       <c r="G37" s="21" t="n">
-        <v>18037</v>
+        <v>17899</v>
       </c>
       <c r="H37" s="22" t="n">
-        <v>18045</v>
+        <v>17480</v>
       </c>
       <c r="I37" s="21" t="n">
-        <v>17934</v>
+        <v>17639</v>
       </c>
       <c r="J37" s="22" t="n">
-        <v>18384</v>
+        <v>17405</v>
       </c>
     </row>
     <row r="38">
@@ -4916,25 +4916,25 @@
         <v>10</v>
       </c>
       <c r="D38" s="21" t="n">
-        <v>17456</v>
+        <v>17083</v>
       </c>
       <c r="E38" s="22" t="n">
-        <v>16617</v>
+        <v>16596</v>
       </c>
       <c r="F38" s="21" t="n">
-        <v>17393</v>
+        <v>16889</v>
       </c>
       <c r="G38" s="21" t="n">
-        <v>17620</v>
+        <v>17490</v>
       </c>
       <c r="H38" s="22" t="n">
-        <v>17921</v>
+        <v>17344</v>
       </c>
       <c r="I38" s="21" t="n">
-        <v>17443</v>
+        <v>17292</v>
       </c>
       <c r="J38" s="22" t="n">
-        <v>17994</v>
+        <v>17039</v>
       </c>
     </row>
     <row r="39">
@@ -4948,25 +4948,25 @@
         <v>10</v>
       </c>
       <c r="D39" s="21" t="n">
-        <v>17402</v>
+        <v>17043</v>
       </c>
       <c r="E39" s="22" t="n">
-        <v>16395</v>
+        <v>16373</v>
       </c>
       <c r="F39" s="21" t="n">
-        <v>17155</v>
+        <v>16886</v>
       </c>
       <c r="G39" s="21" t="n">
-        <v>17689</v>
+        <v>17619</v>
       </c>
       <c r="H39" s="22" t="n">
-        <v>17937</v>
+        <v>17329</v>
       </c>
       <c r="I39" s="21" t="n">
-        <v>17419</v>
+        <v>17217</v>
       </c>
       <c r="J39" s="22" t="n">
-        <v>18118</v>
+        <v>17032</v>
       </c>
     </row>
     <row r="40">
@@ -4980,25 +4980,25 @@
         <v>10</v>
       </c>
       <c r="D40" s="21" t="n">
-        <v>17130</v>
+        <v>16816</v>
       </c>
       <c r="E40" s="22" t="n">
-        <v>16219</v>
+        <v>16199</v>
       </c>
       <c r="F40" s="21" t="n">
-        <v>16993</v>
+        <v>16537</v>
       </c>
       <c r="G40" s="21" t="n">
-        <v>17459</v>
+        <v>17551</v>
       </c>
       <c r="H40" s="22" t="n">
-        <v>17634</v>
+        <v>17032</v>
       </c>
       <c r="I40" s="21" t="n">
-        <v>17187</v>
+        <v>16927</v>
       </c>
       <c r="J40" s="22" t="n">
-        <v>17563</v>
+        <v>16821</v>
       </c>
     </row>
     <row r="41">
@@ -5012,25 +5012,25 @@
         <v>10</v>
       </c>
       <c r="D41" s="21" t="n">
-        <v>16995</v>
+        <v>16700</v>
       </c>
       <c r="E41" s="22" t="n">
-        <v>16007</v>
+        <v>15986</v>
       </c>
       <c r="F41" s="21" t="n">
-        <v>16770</v>
+        <v>16419</v>
       </c>
       <c r="G41" s="21" t="n">
-        <v>17439</v>
+        <v>17491</v>
       </c>
       <c r="H41" s="22" t="n">
-        <v>17401</v>
+        <v>16846</v>
       </c>
       <c r="I41" s="21" t="n">
-        <v>17125</v>
+        <v>16827</v>
       </c>
       <c r="J41" s="22" t="n">
-        <v>17509</v>
+        <v>16821</v>
       </c>
     </row>
     <row r="42">
@@ -5044,25 +5044,25 @@
         <v>11</v>
       </c>
       <c r="D42" s="21" t="n">
-        <v>16923</v>
+        <v>16642</v>
       </c>
       <c r="E42" s="22" t="n">
-        <v>15869</v>
+        <v>15846</v>
       </c>
       <c r="F42" s="21" t="n">
-        <v>16733</v>
+        <v>16239</v>
       </c>
       <c r="G42" s="21" t="n">
-        <v>17395</v>
+        <v>17544</v>
       </c>
       <c r="H42" s="22" t="n">
-        <v>17325</v>
+        <v>16692</v>
       </c>
       <c r="I42" s="21" t="n">
-        <v>17084</v>
+        <v>16922</v>
       </c>
       <c r="J42" s="22" t="n">
-        <v>17432</v>
+        <v>16811</v>
       </c>
     </row>
     <row r="43">
@@ -5076,25 +5076,25 @@
         <v>11</v>
       </c>
       <c r="D43" s="21" t="n">
-        <v>16680</v>
+        <v>16392</v>
       </c>
       <c r="E43" s="22" t="n">
-        <v>15657</v>
+        <v>15634</v>
       </c>
       <c r="F43" s="21" t="n">
-        <v>16562</v>
+        <v>15946</v>
       </c>
       <c r="G43" s="21" t="n">
-        <v>17321</v>
+        <v>17374</v>
       </c>
       <c r="H43" s="22" t="n">
-        <v>17138</v>
+        <v>16454</v>
       </c>
       <c r="I43" s="21" t="n">
-        <v>16622</v>
+        <v>16531</v>
       </c>
       <c r="J43" s="22" t="n">
-        <v>17067</v>
+        <v>16605</v>
       </c>
     </row>
     <row r="44">
@@ -5108,25 +5108,25 @@
         <v>11</v>
       </c>
       <c r="D44" s="21" t="n">
-        <v>16469</v>
+        <v>16154</v>
       </c>
       <c r="E44" s="22" t="n">
-        <v>15418</v>
+        <v>15394</v>
       </c>
       <c r="F44" s="21" t="n">
-        <v>16264</v>
+        <v>15692</v>
       </c>
       <c r="G44" s="21" t="n">
-        <v>17262</v>
+        <v>17351</v>
       </c>
       <c r="H44" s="22" t="n">
-        <v>16905</v>
+        <v>16182</v>
       </c>
       <c r="I44" s="21" t="n">
-        <v>16486</v>
+        <v>16236</v>
       </c>
       <c r="J44" s="22" t="n">
-        <v>16766</v>
+        <v>16246</v>
       </c>
     </row>
     <row r="45">
@@ -5140,25 +5140,25 @@
         <v>11</v>
       </c>
       <c r="D45" s="21" t="n">
-        <v>16067</v>
+        <v>15725</v>
       </c>
       <c r="E45" s="22" t="n">
-        <v>15187</v>
+        <v>15161</v>
       </c>
       <c r="F45" s="21" t="n">
-        <v>15987</v>
+        <v>15384</v>
       </c>
       <c r="G45" s="21" t="n">
         <v>16615</v>
       </c>
       <c r="H45" s="22" t="n">
-        <v>16360</v>
+        <v>15583</v>
       </c>
       <c r="I45" s="21" t="n">
-        <v>16154</v>
+        <v>15905</v>
       </c>
       <c r="J45" s="22" t="n">
-        <v>16337</v>
+        <v>15818</v>
       </c>
     </row>
     <row r="46">
@@ -5172,25 +5172,25 @@
         <v>12</v>
       </c>
       <c r="D46" s="21" t="n">
-        <v>16857</v>
+        <v>16588</v>
       </c>
       <c r="E46" s="22" t="n">
-        <v>15913</v>
+        <v>15882</v>
       </c>
       <c r="F46" s="21" t="n">
-        <v>16584</v>
+        <v>16483</v>
       </c>
       <c r="G46" s="21" t="n">
-        <v>17512</v>
+        <v>17628</v>
       </c>
       <c r="H46" s="22" t="n">
-        <v>17530</v>
+        <v>16765</v>
       </c>
       <c r="I46" s="21" t="n">
-        <v>16803</v>
+        <v>16428</v>
       </c>
       <c r="J46" s="22" t="n">
-        <v>17090</v>
+        <v>16511</v>
       </c>
     </row>
     <row r="47">
@@ -5204,25 +5204,25 @@
         <v>12</v>
       </c>
       <c r="D47" s="21" t="n">
-        <v>16862</v>
+        <v>16558</v>
       </c>
       <c r="E47" s="22" t="n">
-        <v>15884</v>
+        <v>15859</v>
       </c>
       <c r="F47" s="21" t="n">
-        <v>16745</v>
+        <v>16513</v>
       </c>
       <c r="G47" s="21" t="n">
-        <v>17429</v>
+        <v>17379</v>
       </c>
       <c r="H47" s="22" t="n">
-        <v>17486</v>
+        <v>16676</v>
       </c>
       <c r="I47" s="21" t="n">
-        <v>16928</v>
+        <v>16510</v>
       </c>
       <c r="J47" s="22" t="n">
-        <v>16997</v>
+        <v>16580</v>
       </c>
     </row>
     <row r="48">
@@ -5236,25 +5236,25 @@
         <v>12</v>
       </c>
       <c r="D48" s="21" t="n">
-        <v>16496</v>
+        <v>16169</v>
       </c>
       <c r="E48" s="22" t="n">
-        <v>15519</v>
+        <v>15495</v>
       </c>
       <c r="F48" s="21" t="n">
-        <v>16297</v>
+        <v>16039</v>
       </c>
       <c r="G48" s="21" t="n">
-        <v>17365</v>
+        <v>17417</v>
       </c>
       <c r="H48" s="22" t="n">
-        <v>16762</v>
+        <v>15949</v>
       </c>
       <c r="I48" s="21" t="n">
-        <v>16573</v>
+        <v>16047</v>
       </c>
       <c r="J48" s="22" t="n">
-        <v>16714</v>
+        <v>16176</v>
       </c>
     </row>
     <row r="49">
@@ -5268,25 +5268,25 @@
         <v>12</v>
       </c>
       <c r="D49" s="21" t="n">
-        <v>15160</v>
+        <v>14678</v>
       </c>
       <c r="E49" s="22" t="n">
-        <v>14904</v>
+        <v>14880</v>
       </c>
       <c r="F49" s="21" t="n">
-        <v>15106</v>
+        <v>14120</v>
       </c>
       <c r="G49" s="21" t="n">
-        <v>15579</v>
+        <v>15554</v>
       </c>
       <c r="H49" s="22" t="n">
-        <v>15151</v>
+        <v>14375</v>
       </c>
       <c r="I49" s="21" t="n">
-        <v>15130</v>
+        <v>14639</v>
       </c>
       <c r="J49" s="22" t="n">
-        <v>15143</v>
+        <v>14387</v>
       </c>
     </row>
     <row r="50">
@@ -5300,25 +5300,25 @@
         <v>13</v>
       </c>
       <c r="D50" s="21" t="n">
-        <v>14949</v>
+        <v>14387</v>
       </c>
       <c r="E50" s="22" t="n">
-        <v>14644</v>
+        <v>14614</v>
       </c>
       <c r="F50" s="21" t="n">
-        <v>14761</v>
+        <v>13625</v>
       </c>
       <c r="G50" s="21" t="n">
-        <v>15463</v>
+        <v>15337</v>
       </c>
       <c r="H50" s="22" t="n">
-        <v>14873</v>
+        <v>14154</v>
       </c>
       <c r="I50" s="21" t="n">
-        <v>14993</v>
+        <v>14247</v>
       </c>
       <c r="J50" s="22" t="n">
-        <v>15019</v>
+        <v>14237</v>
       </c>
     </row>
     <row r="51">
@@ -5332,25 +5332,25 @@
         <v>13</v>
       </c>
       <c r="D51" s="21" t="n">
-        <v>14416</v>
+        <v>13760</v>
       </c>
       <c r="E51" s="22" t="n">
-        <v>14363</v>
+        <v>14332</v>
       </c>
       <c r="F51" s="21" t="n">
-        <v>14160</v>
+        <v>12955</v>
       </c>
       <c r="G51" s="21" t="n">
-        <v>14764</v>
+        <v>14329</v>
       </c>
       <c r="H51" s="22" t="n">
-        <v>14330</v>
+        <v>13682</v>
       </c>
       <c r="I51" s="21" t="n">
-        <v>14290</v>
+        <v>13554</v>
       </c>
       <c r="J51" s="22" t="n">
-        <v>14587</v>
+        <v>13533</v>
       </c>
     </row>
     <row r="52">
@@ -5364,25 +5364,25 @@
         <v>13</v>
       </c>
       <c r="D52" s="21" t="n">
-        <v>14224</v>
+        <v>13474</v>
       </c>
       <c r="E52" s="22" t="n">
-        <v>14141</v>
+        <v>14109</v>
       </c>
       <c r="F52" s="21" t="n">
-        <v>13968</v>
+        <v>12843</v>
       </c>
       <c r="G52" s="21" t="n">
-        <v>14563</v>
+        <v>13998</v>
       </c>
       <c r="H52" s="22" t="n">
-        <v>14134</v>
+        <v>13398</v>
       </c>
       <c r="I52" s="21" t="n">
-        <v>14100</v>
+        <v>13130</v>
       </c>
       <c r="J52" s="22" t="n">
-        <v>14447</v>
+        <v>13173</v>
       </c>
     </row>
     <row r="53">
@@ -5396,25 +5396,25 @@
         <v>13</v>
       </c>
       <c r="D53" s="21" t="n">
-        <v>14156</v>
+        <v>13377</v>
       </c>
       <c r="E53" s="22" t="n">
-        <v>14046</v>
+        <v>14012</v>
       </c>
       <c r="F53" s="21" t="n">
-        <v>13929</v>
+        <v>12665</v>
       </c>
       <c r="G53" s="21" t="n">
-        <v>14538</v>
+        <v>13959</v>
       </c>
       <c r="H53" s="22" t="n">
-        <v>14097</v>
+        <v>13315</v>
       </c>
       <c r="I53" s="21" t="n">
-        <v>13930</v>
+        <v>12986</v>
       </c>
       <c r="J53" s="22" t="n">
-        <v>14408</v>
+        <v>13129</v>
       </c>
     </row>
     <row r="54">
@@ -5428,25 +5428,25 @@
         <v>14</v>
       </c>
       <c r="D54" s="21" t="n">
-        <v>14240</v>
+        <v>13568</v>
       </c>
       <c r="E54" s="22" t="n">
-        <v>14179</v>
+        <v>14143</v>
       </c>
       <c r="F54" s="21" t="n">
-        <v>14000</v>
+        <v>13079</v>
       </c>
       <c r="G54" s="21" t="n">
-        <v>14601</v>
+        <v>14013</v>
       </c>
       <c r="H54" s="22" t="n">
-        <v>14239</v>
+        <v>13522</v>
       </c>
       <c r="I54" s="21" t="n">
-        <v>14047</v>
+        <v>13116</v>
       </c>
       <c r="J54" s="22" t="n">
-        <v>14381</v>
+        <v>13359</v>
       </c>
     </row>
     <row r="55">
@@ -5460,25 +5460,25 @@
         <v>14</v>
       </c>
       <c r="D55" s="21" t="n">
-        <v>14414</v>
+        <v>13845</v>
       </c>
       <c r="E55" s="22" t="n">
-        <v>14274</v>
+        <v>14239</v>
       </c>
       <c r="F55" s="21" t="n">
-        <v>14200</v>
+        <v>13296</v>
       </c>
       <c r="G55" s="21" t="n">
-        <v>14838</v>
+        <v>14501</v>
       </c>
       <c r="H55" s="22" t="n">
-        <v>14427</v>
+        <v>13684</v>
       </c>
       <c r="I55" s="21" t="n">
-        <v>14147</v>
+        <v>13542</v>
       </c>
       <c r="J55" s="22" t="n">
-        <v>14618</v>
+        <v>13662</v>
       </c>
     </row>
     <row r="56">
@@ -5492,25 +5492,25 @@
         <v>14</v>
       </c>
       <c r="D56" s="21" t="n">
-        <v>14609</v>
+        <v>14009</v>
       </c>
       <c r="E56" s="22" t="n">
-        <v>14394</v>
+        <v>14360</v>
       </c>
       <c r="F56" s="21" t="n">
-        <v>14403</v>
+        <v>13287</v>
       </c>
       <c r="G56" s="21" t="n">
-        <v>15025</v>
+        <v>14702</v>
       </c>
       <c r="H56" s="22" t="n">
-        <v>14595</v>
+        <v>13796</v>
       </c>
       <c r="I56" s="21" t="n">
-        <v>14579</v>
+        <v>13900</v>
       </c>
       <c r="J56" s="22" t="n">
-        <v>14703</v>
+        <v>13877</v>
       </c>
     </row>
     <row r="57">
@@ -5524,25 +5524,25 @@
         <v>14</v>
       </c>
       <c r="D57" s="21" t="n">
-        <v>14810</v>
+        <v>14216</v>
       </c>
       <c r="E57" s="22" t="n">
-        <v>14470</v>
+        <v>14436</v>
       </c>
       <c r="F57" s="21" t="n">
-        <v>14691</v>
+        <v>13641</v>
       </c>
       <c r="G57" s="21" t="n">
-        <v>15395</v>
+        <v>15132</v>
       </c>
       <c r="H57" s="22" t="n">
-        <v>14747</v>
+        <v>13957</v>
       </c>
       <c r="I57" s="21" t="n">
-        <v>14731</v>
+        <v>13944</v>
       </c>
       <c r="J57" s="22" t="n">
-        <v>14890</v>
+        <v>14071</v>
       </c>
     </row>
     <row r="58">
@@ -5556,25 +5556,25 @@
         <v>15</v>
       </c>
       <c r="D58" s="21" t="n">
-        <v>14883</v>
+        <v>14344</v>
       </c>
       <c r="E58" s="22" t="n">
-        <v>14612</v>
+        <v>14579</v>
       </c>
       <c r="F58" s="21" t="n">
-        <v>14757</v>
+        <v>13777</v>
       </c>
       <c r="G58" s="21" t="n">
-        <v>15482</v>
+        <v>15390</v>
       </c>
       <c r="H58" s="22" t="n">
-        <v>14907</v>
+        <v>14119</v>
       </c>
       <c r="I58" s="21" t="n">
-        <v>14738</v>
+        <v>13980</v>
       </c>
       <c r="J58" s="22" t="n">
-        <v>14856</v>
+        <v>14093</v>
       </c>
     </row>
     <row r="59">
@@ -5588,25 +5588,25 @@
         <v>15</v>
       </c>
       <c r="D59" s="21" t="n">
-        <v>15020</v>
+        <v>14525</v>
       </c>
       <c r="E59" s="22" t="n">
-        <v>14745</v>
+        <v>14712</v>
       </c>
       <c r="F59" s="21" t="n">
-        <v>14904</v>
+        <v>14137</v>
       </c>
       <c r="G59" s="21" t="n">
-        <v>15527</v>
+        <v>15485</v>
       </c>
       <c r="H59" s="22" t="n">
-        <v>15147</v>
+        <v>14318</v>
       </c>
       <c r="I59" s="21" t="n">
-        <v>14837</v>
+        <v>14262</v>
       </c>
       <c r="J59" s="22" t="n">
-        <v>15025</v>
+        <v>14124</v>
       </c>
     </row>
     <row r="60">
@@ -5620,25 +5620,25 @@
         <v>15</v>
       </c>
       <c r="D60" s="21" t="n">
-        <v>15106</v>
+        <v>14662</v>
       </c>
       <c r="E60" s="22" t="n">
-        <v>14802</v>
+        <v>14771</v>
       </c>
       <c r="F60" s="21" t="n">
-        <v>15083</v>
+        <v>14509</v>
       </c>
       <c r="G60" s="21" t="n">
-        <v>15527</v>
+        <v>15485</v>
       </c>
       <c r="H60" s="22" t="n">
-        <v>15210</v>
+        <v>14334</v>
       </c>
       <c r="I60" s="21" t="n">
-        <v>15056</v>
+        <v>14536</v>
       </c>
       <c r="J60" s="22" t="n">
-        <v>15031</v>
+        <v>14235</v>
       </c>
     </row>
     <row r="61">
@@ -5652,25 +5652,25 @@
         <v>15</v>
       </c>
       <c r="D61" s="21" t="n">
-        <v>15399</v>
+        <v>14875</v>
       </c>
       <c r="E61" s="22" t="n">
-        <v>14879</v>
+        <v>14848</v>
       </c>
       <c r="F61" s="21" t="n">
-        <v>15454</v>
+        <v>14437</v>
       </c>
       <c r="G61" s="21" t="n">
-        <v>15552</v>
+        <v>15475</v>
       </c>
       <c r="H61" s="22" t="n">
-        <v>15438</v>
+        <v>14623</v>
       </c>
       <c r="I61" s="21" t="n">
-        <v>15633</v>
+        <v>15078</v>
       </c>
       <c r="J61" s="22" t="n">
-        <v>15575</v>
+        <v>14763</v>
       </c>
     </row>
     <row r="62">
@@ -5684,25 +5684,25 @@
         <v>16</v>
       </c>
       <c r="D62" s="21" t="n">
-        <v>15444</v>
+        <v>14975</v>
       </c>
       <c r="E62" s="22" t="n">
-        <v>14641</v>
+        <v>14610</v>
       </c>
       <c r="F62" s="21" t="n">
-        <v>15546</v>
+        <v>14683</v>
       </c>
       <c r="G62" s="21" t="n">
-        <v>15640</v>
+        <v>15609</v>
       </c>
       <c r="H62" s="22" t="n">
-        <v>15578</v>
+        <v>14739</v>
       </c>
       <c r="I62" s="21" t="n">
-        <v>15772</v>
+        <v>15339</v>
       </c>
       <c r="J62" s="22" t="n">
-        <v>15701</v>
+        <v>14933</v>
       </c>
     </row>
     <row r="63">
@@ -5716,25 +5716,25 @@
         <v>16</v>
       </c>
       <c r="D63" s="21" t="n">
-        <v>15558</v>
+        <v>15097</v>
       </c>
       <c r="E63" s="22" t="n">
-        <v>14724</v>
+        <v>14695</v>
       </c>
       <c r="F63" s="21" t="n">
-        <v>15700</v>
+        <v>14942</v>
       </c>
       <c r="G63" s="21" t="n">
-        <v>15640</v>
+        <v>15609</v>
       </c>
       <c r="H63" s="22" t="n">
-        <v>15606</v>
+        <v>14833</v>
       </c>
       <c r="I63" s="21" t="n">
-        <v>15997</v>
+        <v>15380</v>
       </c>
       <c r="J63" s="22" t="n">
-        <v>15903</v>
+        <v>15194</v>
       </c>
     </row>
     <row r="64">
@@ -5748,25 +5748,25 @@
         <v>16</v>
       </c>
       <c r="D64" s="21" t="n">
-        <v>15973</v>
+        <v>15525</v>
       </c>
       <c r="E64" s="22" t="n">
-        <v>14896</v>
+        <v>14866</v>
       </c>
       <c r="F64" s="21" t="n">
-        <v>16460</v>
+        <v>15751</v>
       </c>
       <c r="G64" s="21" t="n">
-        <v>15715</v>
+        <v>15714</v>
       </c>
       <c r="H64" s="22" t="n">
-        <v>16069</v>
+        <v>15298</v>
       </c>
       <c r="I64" s="21" t="n">
-        <v>16545</v>
+        <v>15935</v>
       </c>
       <c r="J64" s="22" t="n">
-        <v>16449</v>
+        <v>15739</v>
       </c>
     </row>
     <row r="65">
@@ -5780,25 +5780,25 @@
         <v>16</v>
       </c>
       <c r="D65" s="21" t="n">
-        <v>16856</v>
+        <v>16333</v>
       </c>
       <c r="E65" s="22" t="n">
-        <v>15211</v>
+        <v>15182</v>
       </c>
       <c r="F65" s="21" t="n">
-        <v>17249</v>
+        <v>16423</v>
       </c>
       <c r="G65" s="21" t="n">
-        <v>17465</v>
+        <v>17392</v>
       </c>
       <c r="H65" s="22" t="n">
-        <v>16842</v>
+        <v>16033</v>
       </c>
       <c r="I65" s="21" t="n">
-        <v>17368</v>
+        <v>16783</v>
       </c>
       <c r="J65" s="22" t="n">
-        <v>17397</v>
+        <v>16431</v>
       </c>
     </row>
     <row r="66">
@@ -5812,25 +5812,25 @@
         <v>17</v>
       </c>
       <c r="D66" s="21" t="n">
-        <v>17030</v>
+        <v>16644</v>
       </c>
       <c r="E66" s="22" t="n">
-        <v>15361</v>
+        <v>15337</v>
       </c>
       <c r="F66" s="21" t="n">
-        <v>17511</v>
+        <v>16663</v>
       </c>
       <c r="G66" s="21" t="n">
-        <v>17511</v>
+        <v>17524</v>
       </c>
       <c r="H66" s="22" t="n">
-        <v>17166</v>
+        <v>16495</v>
       </c>
       <c r="I66" s="21" t="n">
-        <v>17619</v>
+        <v>17310</v>
       </c>
       <c r="J66" s="22" t="n">
-        <v>17438</v>
+        <v>16852</v>
       </c>
     </row>
     <row r="67">
@@ -5844,25 +5844,25 @@
         <v>17</v>
       </c>
       <c r="D67" s="21" t="n">
-        <v>17205</v>
+        <v>16848</v>
       </c>
       <c r="E67" s="22" t="n">
-        <v>15733</v>
+        <v>15711</v>
       </c>
       <c r="F67" s="21" t="n">
-        <v>17694</v>
+        <v>17117</v>
       </c>
       <c r="G67" s="21" t="n">
-        <v>17476</v>
+        <v>17473</v>
       </c>
       <c r="H67" s="22" t="n">
-        <v>17326</v>
+        <v>16703</v>
       </c>
       <c r="I67" s="21" t="n">
-        <v>17816</v>
+        <v>17314</v>
       </c>
       <c r="J67" s="22" t="n">
-        <v>17562</v>
+        <v>17044</v>
       </c>
     </row>
     <row r="68">
@@ -5876,25 +5876,25 @@
         <v>17</v>
       </c>
       <c r="D68" s="21" t="n">
-        <v>17297</v>
+        <v>16990</v>
       </c>
       <c r="E68" s="22" t="n">
-        <v>16088</v>
+        <v>16066</v>
       </c>
       <c r="F68" s="21" t="n">
-        <v>17654</v>
+        <v>17166</v>
       </c>
       <c r="G68" s="21" t="n">
-        <v>17500</v>
+        <v>17497</v>
       </c>
       <c r="H68" s="22" t="n">
-        <v>17476</v>
+        <v>16926</v>
       </c>
       <c r="I68" s="21" t="n">
-        <v>17810</v>
+        <v>17436</v>
       </c>
       <c r="J68" s="22" t="n">
-        <v>17578</v>
+        <v>17078</v>
       </c>
     </row>
     <row r="69">
@@ -5908,25 +5908,25 @@
         <v>17</v>
       </c>
       <c r="D69" s="21" t="n">
-        <v>17516</v>
+        <v>17147</v>
       </c>
       <c r="E69" s="22" t="n">
-        <v>16416</v>
+        <v>16395</v>
       </c>
       <c r="F69" s="21" t="n">
-        <v>17971</v>
+        <v>17343</v>
       </c>
       <c r="G69" s="21" t="n">
-        <v>17457</v>
+        <v>17406</v>
       </c>
       <c r="H69" s="22" t="n">
-        <v>17881</v>
+        <v>17369</v>
       </c>
       <c r="I69" s="21" t="n">
-        <v>17934</v>
+        <v>17446</v>
       </c>
       <c r="J69" s="22" t="n">
-        <v>17750</v>
+        <v>17141</v>
       </c>
     </row>
     <row r="70">
@@ -5940,25 +5940,25 @@
         <v>18</v>
       </c>
       <c r="D70" s="21" t="n">
-        <v>17406</v>
+        <v>17071</v>
       </c>
       <c r="E70" s="22" t="n">
-        <v>16715</v>
+        <v>16696</v>
       </c>
       <c r="F70" s="21" t="n">
-        <v>17736</v>
+        <v>17280</v>
       </c>
       <c r="G70" s="21" t="n">
-        <v>17211</v>
+        <v>17126</v>
       </c>
       <c r="H70" s="22" t="n">
-        <v>17964</v>
+        <v>17416</v>
       </c>
       <c r="I70" s="21" t="n">
-        <v>17575</v>
+        <v>17080</v>
       </c>
       <c r="J70" s="22" t="n">
-        <v>17465</v>
+        <v>16955</v>
       </c>
     </row>
     <row r="71">
@@ -5972,25 +5972,25 @@
         <v>18</v>
       </c>
       <c r="D71" s="21" t="n">
-        <v>17747</v>
+        <v>17325</v>
       </c>
       <c r="E71" s="22" t="n">
-        <v>16940</v>
+        <v>16920</v>
       </c>
       <c r="F71" s="21" t="n">
-        <v>18525</v>
+        <v>17773</v>
       </c>
       <c r="G71" s="21" t="n">
-        <v>17329</v>
+        <v>17243</v>
       </c>
       <c r="H71" s="22" t="n">
-        <v>18192</v>
+        <v>17639</v>
       </c>
       <c r="I71" s="21" t="n">
-        <v>17913</v>
+        <v>17409</v>
       </c>
       <c r="J71" s="22" t="n">
-        <v>17828</v>
+        <v>17100</v>
       </c>
     </row>
     <row r="72">
@@ -6004,25 +6004,25 @@
         <v>18</v>
       </c>
       <c r="D72" s="21" t="n">
-        <v>17736</v>
+        <v>17358</v>
       </c>
       <c r="E72" s="22" t="n">
-        <v>17110</v>
+        <v>17089</v>
       </c>
       <c r="F72" s="21" t="n">
-        <v>18271</v>
+        <v>17583</v>
       </c>
       <c r="G72" s="21" t="n">
-        <v>17320</v>
+        <v>17368</v>
       </c>
       <c r="H72" s="22" t="n">
-        <v>18154</v>
+        <v>17597</v>
       </c>
       <c r="I72" s="21" t="n">
-        <v>17873</v>
+        <v>17454</v>
       </c>
       <c r="J72" s="22" t="n">
-        <v>17894</v>
+        <v>17150</v>
       </c>
     </row>
     <row r="73">
@@ -6036,25 +6036,25 @@
         <v>18</v>
       </c>
       <c r="D73" s="21" t="n">
-        <v>17566</v>
+        <v>17036</v>
       </c>
       <c r="E73" s="22" t="n">
-        <v>17157</v>
+        <v>17137</v>
       </c>
       <c r="F73" s="21" t="n">
-        <v>18117</v>
+        <v>17089</v>
       </c>
       <c r="G73" s="21" t="n">
-        <v>17025</v>
+        <v>16638</v>
       </c>
       <c r="H73" s="22" t="n">
-        <v>17811</v>
+        <v>17216</v>
       </c>
       <c r="I73" s="21" t="n">
-        <v>17765</v>
+        <v>17222</v>
       </c>
       <c r="J73" s="22" t="n">
-        <v>17660</v>
+        <v>16924</v>
       </c>
     </row>
     <row r="74">
@@ -6068,25 +6068,25 @@
         <v>19</v>
       </c>
       <c r="D74" s="21" t="n">
-        <v>17370</v>
+        <v>16891</v>
       </c>
       <c r="E74" s="22" t="n">
-        <v>17121</v>
+        <v>17101</v>
       </c>
       <c r="F74" s="21" t="n">
-        <v>17842</v>
+        <v>17155</v>
       </c>
       <c r="G74" s="21" t="n">
-        <v>16915</v>
+        <v>16443</v>
       </c>
       <c r="H74" s="22" t="n">
-        <v>17331</v>
+        <v>16831</v>
       </c>
       <c r="I74" s="21" t="n">
-        <v>17447</v>
+        <v>17071</v>
       </c>
       <c r="J74" s="22" t="n">
-        <v>17628</v>
+        <v>16691</v>
       </c>
     </row>
     <row r="75">
@@ -6100,25 +6100,25 @@
         <v>19</v>
       </c>
       <c r="D75" s="21" t="n">
-        <v>17133</v>
+        <v>16694</v>
       </c>
       <c r="E75" s="22" t="n">
-        <v>16904</v>
+        <v>16882</v>
       </c>
       <c r="F75" s="21" t="n">
-        <v>17397</v>
+        <v>16941</v>
       </c>
       <c r="G75" s="21" t="n">
-        <v>16925</v>
+        <v>16437</v>
       </c>
       <c r="H75" s="22" t="n">
-        <v>16915</v>
+        <v>16451</v>
       </c>
       <c r="I75" s="21" t="n">
-        <v>17322</v>
+        <v>16872</v>
       </c>
       <c r="J75" s="22" t="n">
-        <v>17375</v>
+        <v>16505</v>
       </c>
     </row>
     <row r="76">
@@ -6132,25 +6132,25 @@
         <v>19</v>
       </c>
       <c r="D76" s="21" t="n">
-        <v>16690</v>
+        <v>16244</v>
       </c>
       <c r="E76" s="22" t="n">
-        <v>16650</v>
+        <v>16628</v>
       </c>
       <c r="F76" s="21" t="n">
-        <v>16951</v>
+        <v>16602</v>
       </c>
       <c r="G76" s="21" t="n">
-        <v>16614</v>
+        <v>15981</v>
       </c>
       <c r="H76" s="22" t="n">
-        <v>16398</v>
+        <v>15939</v>
       </c>
       <c r="I76" s="21" t="n">
-        <v>16745</v>
+        <v>16220</v>
       </c>
       <c r="J76" s="22" t="n">
-        <v>16760</v>
+        <v>15956</v>
       </c>
     </row>
     <row r="77">
@@ -6164,25 +6164,25 @@
         <v>19</v>
       </c>
       <c r="D77" s="21" t="n">
-        <v>16355</v>
+        <v>15838</v>
       </c>
       <c r="E77" s="22" t="n">
-        <v>16360</v>
+        <v>16337</v>
       </c>
       <c r="F77" s="21" t="n">
-        <v>16552</v>
+        <v>16219</v>
       </c>
       <c r="G77" s="21" t="n">
-        <v>16389</v>
+        <v>15443</v>
       </c>
       <c r="H77" s="22" t="n">
-        <v>15862</v>
+        <v>15438</v>
       </c>
       <c r="I77" s="21" t="n">
-        <v>16505</v>
+        <v>15990</v>
       </c>
       <c r="J77" s="22" t="n">
-        <v>16411</v>
+        <v>15428</v>
       </c>
     </row>
     <row r="78">
@@ -6196,25 +6196,25 @@
         <v>20</v>
       </c>
       <c r="D78" s="21" t="n">
-        <v>15951</v>
+        <v>15238</v>
       </c>
       <c r="E78" s="22" t="n">
-        <v>16056</v>
+        <v>16034</v>
       </c>
       <c r="F78" s="21" t="n">
-        <v>15920</v>
+        <v>15306</v>
       </c>
       <c r="G78" s="21" t="n">
-        <v>16318</v>
+        <v>14996</v>
       </c>
       <c r="H78" s="22" t="n">
-        <v>15357</v>
+        <v>14929</v>
       </c>
       <c r="I78" s="21" t="n">
-        <v>15929</v>
+        <v>15093</v>
       </c>
       <c r="J78" s="22" t="n">
-        <v>16032</v>
+        <v>14818</v>
       </c>
     </row>
     <row r="79">
@@ -6228,25 +6228,25 @@
         <v>20</v>
       </c>
       <c r="D79" s="21" t="n">
-        <v>15497</v>
+        <v>14722</v>
       </c>
       <c r="E79" s="22" t="n">
-        <v>15735</v>
+        <v>15710</v>
       </c>
       <c r="F79" s="21" t="n">
-        <v>15454</v>
+        <v>14848</v>
       </c>
       <c r="G79" s="21" t="n">
-        <v>16178</v>
+        <v>14924</v>
       </c>
       <c r="H79" s="22" t="n">
-        <v>14933</v>
+        <v>14487</v>
       </c>
       <c r="I79" s="21" t="n">
-        <v>14891</v>
+        <v>13984</v>
       </c>
       <c r="J79" s="22" t="n">
-        <v>15646</v>
+        <v>14053</v>
       </c>
     </row>
     <row r="80">
@@ -6260,25 +6260,25 @@
         <v>20</v>
       </c>
       <c r="D80" s="21" t="n">
-        <v>14798</v>
+        <v>13965</v>
       </c>
       <c r="E80" s="22" t="n">
-        <v>15465</v>
+        <v>15439</v>
       </c>
       <c r="F80" s="21" t="n">
-        <v>14883</v>
+        <v>14066</v>
       </c>
       <c r="G80" s="21" t="n">
-        <v>14530</v>
+        <v>13539</v>
       </c>
       <c r="H80" s="22" t="n">
-        <v>14521</v>
+        <v>14005</v>
       </c>
       <c r="I80" s="21" t="n">
-        <v>13943</v>
+        <v>12917</v>
       </c>
       <c r="J80" s="22" t="n">
-        <v>15239</v>
+        <v>13413</v>
       </c>
     </row>
     <row r="81">
@@ -6292,25 +6292,25 @@
         <v>20</v>
       </c>
       <c r="D81" s="21" t="n">
-        <v>14483</v>
+        <v>13601</v>
       </c>
       <c r="E81" s="22" t="n">
-        <v>15152</v>
+        <v>15125</v>
       </c>
       <c r="F81" s="21" t="n">
-        <v>14527</v>
+        <v>13864</v>
       </c>
       <c r="G81" s="21" t="n">
-        <v>13650</v>
+        <v>12551</v>
       </c>
       <c r="H81" s="22" t="n">
-        <v>14440</v>
+        <v>13757</v>
       </c>
       <c r="I81" s="21" t="n">
-        <v>13741</v>
+        <v>12620</v>
       </c>
       <c r="J81" s="22" t="n">
-        <v>15223</v>
+        <v>13301</v>
       </c>
     </row>
     <row r="82">
@@ -6324,25 +6324,25 @@
         <v>21</v>
       </c>
       <c r="D82" s="21" t="n">
-        <v>14280</v>
+        <v>13316</v>
       </c>
       <c r="E82" s="22" t="n">
-        <v>14977</v>
+        <v>14950</v>
       </c>
       <c r="F82" s="21" t="n">
-        <v>14115</v>
+        <v>13794</v>
       </c>
       <c r="G82" s="21" t="n">
-        <v>13320</v>
+        <v>12144</v>
       </c>
       <c r="H82" s="22" t="n">
-        <v>14254</v>
+        <v>13444</v>
       </c>
       <c r="I82" s="21" t="n">
-        <v>13649</v>
+        <v>12299</v>
       </c>
       <c r="J82" s="22" t="n">
-        <v>15209</v>
+        <v>12841</v>
       </c>
     </row>
     <row r="83">
@@ -6356,25 +6356,25 @@
         <v>21</v>
       </c>
       <c r="D83" s="21" t="n">
-        <v>14308</v>
+        <v>13355</v>
       </c>
       <c r="E83" s="22" t="n">
-        <v>14936</v>
+        <v>14906</v>
       </c>
       <c r="F83" s="21" t="n">
-        <v>14348</v>
+        <v>13635</v>
       </c>
       <c r="G83" s="21" t="n">
-        <v>13324</v>
+        <v>12190</v>
       </c>
       <c r="H83" s="22" t="n">
-        <v>14338</v>
+        <v>13575</v>
       </c>
       <c r="I83" s="21" t="n">
-        <v>13736</v>
+        <v>12457</v>
       </c>
       <c r="J83" s="22" t="n">
-        <v>15028</v>
+        <v>12984</v>
       </c>
     </row>
     <row r="84">
@@ -6388,25 +6388,25 @@
         <v>21</v>
       </c>
       <c r="D84" s="21" t="n">
-        <v>14265</v>
+        <v>13447</v>
       </c>
       <c r="E84" s="22" t="n">
-        <v>14926</v>
+        <v>14895</v>
       </c>
       <c r="F84" s="21" t="n">
-        <v>14119</v>
+        <v>13483</v>
       </c>
       <c r="G84" s="21" t="n">
-        <v>13465</v>
+        <v>12549</v>
       </c>
       <c r="H84" s="22" t="n">
-        <v>14179</v>
+        <v>13519</v>
       </c>
       <c r="I84" s="21" t="n">
-        <v>13737</v>
+        <v>12719</v>
       </c>
       <c r="J84" s="22" t="n">
-        <v>15006</v>
+        <v>13148</v>
       </c>
     </row>
     <row r="85">
@@ -6420,25 +6420,25 @@
         <v>21</v>
       </c>
       <c r="D85" s="21" t="n">
-        <v>14484</v>
+        <v>13704</v>
       </c>
       <c r="E85" s="22" t="n">
-        <v>14938</v>
+        <v>14907</v>
       </c>
       <c r="F85" s="21" t="n">
-        <v>14124</v>
+        <v>13525</v>
       </c>
       <c r="G85" s="21" t="n">
-        <v>14565</v>
+        <v>13450</v>
       </c>
       <c r="H85" s="22" t="n">
-        <v>14138</v>
+        <v>13599</v>
       </c>
       <c r="I85" s="21" t="n">
-        <v>13991</v>
+        <v>13110</v>
       </c>
       <c r="J85" s="22" t="n">
-        <v>14996</v>
+        <v>13291</v>
       </c>
     </row>
     <row r="86">
@@ -6452,25 +6452,25 @@
         <v>22</v>
       </c>
       <c r="D86" s="21" t="n">
-        <v>15016</v>
+        <v>14257</v>
       </c>
       <c r="E86" s="22" t="n">
-        <v>15034</v>
+        <v>15002</v>
       </c>
       <c r="F86" s="21" t="n">
-        <v>14544</v>
+        <v>13957</v>
       </c>
       <c r="G86" s="21" t="n">
-        <v>16079</v>
+        <v>14805</v>
       </c>
       <c r="H86" s="22" t="n">
-        <v>14289</v>
+        <v>13831</v>
       </c>
       <c r="I86" s="21" t="n">
-        <v>14834</v>
+        <v>13894</v>
       </c>
       <c r="J86" s="22" t="n">
-        <v>15212</v>
+        <v>13780</v>
       </c>
     </row>
     <row r="87">
@@ -6484,25 +6484,25 @@
         <v>22</v>
       </c>
       <c r="D87" s="21" t="n">
-        <v>14342</v>
+        <v>13445</v>
       </c>
       <c r="E87" s="22" t="n">
-        <v>14916</v>
+        <v>14887</v>
       </c>
       <c r="F87" s="21" t="n">
-        <v>14219</v>
+        <v>13366</v>
       </c>
       <c r="G87" s="21" t="n">
-        <v>13721</v>
+        <v>12621</v>
       </c>
       <c r="H87" s="22" t="n">
-        <v>14087</v>
+        <v>13495</v>
       </c>
       <c r="I87" s="21" t="n">
-        <v>13841</v>
+        <v>12850</v>
       </c>
       <c r="J87" s="22" t="n">
-        <v>15113</v>
+        <v>13084</v>
       </c>
     </row>
     <row r="88">
@@ -6516,25 +6516,25 @@
         <v>22</v>
       </c>
       <c r="D88" s="21" t="n">
-        <v>14233</v>
+        <v>13198</v>
       </c>
       <c r="E88" s="22" t="n">
-        <v>14761</v>
+        <v>14731</v>
       </c>
       <c r="F88" s="21" t="n">
-        <v>14085</v>
+        <v>13270</v>
       </c>
       <c r="G88" s="21" t="n">
-        <v>13334</v>
+        <v>12182</v>
       </c>
       <c r="H88" s="22" t="n">
-        <v>14064</v>
+        <v>13387</v>
       </c>
       <c r="I88" s="21" t="n">
-        <v>13725</v>
+        <v>12398</v>
       </c>
       <c r="J88" s="22" t="n">
-        <v>15303</v>
+        <v>12842</v>
       </c>
     </row>
     <row r="89">
@@ -6548,25 +6548,25 @@
         <v>22</v>
       </c>
       <c r="D89" s="21" t="n">
-        <v>14182</v>
+        <v>13121</v>
       </c>
       <c r="E89" s="22" t="n">
-        <v>14618</v>
+        <v>14587</v>
       </c>
       <c r="F89" s="21" t="n">
-        <v>14084</v>
+        <v>13231</v>
       </c>
       <c r="G89" s="21" t="n">
-        <v>13339</v>
+        <v>12178</v>
       </c>
       <c r="H89" s="22" t="n">
-        <v>13970</v>
+        <v>13189</v>
       </c>
       <c r="I89" s="21" t="n">
-        <v>13745</v>
+        <v>12415</v>
       </c>
       <c r="J89" s="22" t="n">
-        <v>15228</v>
+        <v>12749</v>
       </c>
     </row>
     <row r="90">
@@ -6580,25 +6580,25 @@
         <v>23</v>
       </c>
       <c r="D90" s="21" t="n">
-        <v>14158</v>
+        <v>13071</v>
       </c>
       <c r="E90" s="22" t="n">
-        <v>14553</v>
+        <v>14523</v>
       </c>
       <c r="F90" s="21" t="n">
-        <v>14074</v>
+        <v>13215</v>
       </c>
       <c r="G90" s="21" t="n">
-        <v>13371</v>
+        <v>12178</v>
       </c>
       <c r="H90" s="22" t="n">
-        <v>13915</v>
+        <v>13121</v>
       </c>
       <c r="I90" s="21" t="n">
-        <v>13723</v>
+        <v>12264</v>
       </c>
       <c r="J90" s="22" t="n">
-        <v>15208</v>
+        <v>12748</v>
       </c>
     </row>
     <row r="91">
@@ -6612,25 +6612,25 @@
         <v>23</v>
       </c>
       <c r="D91" s="21" t="n">
-        <v>14165</v>
+        <v>13135</v>
       </c>
       <c r="E91" s="22" t="n">
-        <v>14566</v>
+        <v>14532</v>
       </c>
       <c r="F91" s="21" t="n">
-        <v>13989</v>
+        <v>13044</v>
       </c>
       <c r="G91" s="21" t="n">
-        <v>13361</v>
+        <v>12077</v>
       </c>
       <c r="H91" s="22" t="n">
-        <v>14103</v>
+        <v>13409</v>
       </c>
       <c r="I91" s="21" t="n">
-        <v>13766</v>
+        <v>12507</v>
       </c>
       <c r="J91" s="22" t="n">
-        <v>15122</v>
+        <v>12917</v>
       </c>
     </row>
     <row r="92">
@@ -6644,25 +6644,25 @@
         <v>23</v>
       </c>
       <c r="D92" s="21" t="n">
-        <v>14149</v>
+        <v>13169</v>
       </c>
       <c r="E92" s="22" t="n">
-        <v>14565</v>
+        <v>14531</v>
       </c>
       <c r="F92" s="21" t="n">
-        <v>14013</v>
+        <v>13434</v>
       </c>
       <c r="G92" s="21" t="n">
-        <v>13084</v>
+        <v>11875</v>
       </c>
       <c r="H92" s="22" t="n">
-        <v>14169</v>
+        <v>13500</v>
       </c>
       <c r="I92" s="21" t="n">
-        <v>13815</v>
+        <v>12434</v>
       </c>
       <c r="J92" s="22" t="n">
-        <v>15176</v>
+        <v>12931</v>
       </c>
     </row>
     <row r="93">
@@ -6676,25 +6676,25 @@
         <v>23</v>
       </c>
       <c r="D93" s="21" t="n">
-        <v>14024</v>
+        <v>13295</v>
       </c>
       <c r="E93" s="22" t="n">
-        <v>14574</v>
+        <v>14540</v>
       </c>
       <c r="F93" s="21" t="n">
-        <v>13887</v>
+        <v>13381</v>
       </c>
       <c r="G93" s="21" t="n">
-        <v>12948</v>
+        <v>12212</v>
       </c>
       <c r="H93" s="22" t="n">
-        <v>14281</v>
+        <v>13533</v>
       </c>
       <c r="I93" s="21" t="n">
-        <v>13545</v>
+        <v>12680</v>
       </c>
       <c r="J93" s="22" t="n">
-        <v>14824</v>
+        <v>13139</v>
       </c>
     </row>
     <row r="94">
@@ -6708,25 +6708,25 @@
         <v>24</v>
       </c>
       <c r="D94" s="21" t="n">
-        <v>14217</v>
+        <v>13475</v>
       </c>
       <c r="E94" s="22" t="n">
-        <v>14652</v>
+        <v>14618</v>
       </c>
       <c r="F94" s="21" t="n">
-        <v>14021</v>
+        <v>13215</v>
       </c>
       <c r="G94" s="21" t="n">
-        <v>13803</v>
+        <v>13405</v>
       </c>
       <c r="H94" s="22" t="n">
-        <v>14267</v>
+        <v>13543</v>
       </c>
       <c r="I94" s="21" t="n">
-        <v>13703</v>
+        <v>12856</v>
       </c>
       <c r="J94" s="22" t="n">
-        <v>14755</v>
+        <v>12901</v>
       </c>
     </row>
     <row r="95">
@@ -6740,25 +6740,25 @@
         <v>24</v>
       </c>
       <c r="D95" s="21" t="n">
-        <v>13698</v>
+        <v>12856</v>
       </c>
       <c r="E95" s="22" t="n">
-        <v>14542</v>
+        <v>14511</v>
       </c>
       <c r="F95" s="21" t="n">
-        <v>13798</v>
+        <v>12882</v>
       </c>
       <c r="G95" s="21" t="n">
-        <v>12147</v>
+        <v>11642</v>
       </c>
       <c r="H95" s="22" t="n">
-        <v>14113</v>
+        <v>13310</v>
       </c>
       <c r="I95" s="21" t="n">
-        <v>13353</v>
+        <v>11992</v>
       </c>
       <c r="J95" s="22" t="n">
-        <v>14100</v>
+        <v>12427</v>
       </c>
     </row>
     <row r="96">
@@ -6772,25 +6772,25 @@
         <v>24</v>
       </c>
       <c r="D96" s="21" t="n">
-        <v>13526</v>
+        <v>12744</v>
       </c>
       <c r="E96" s="22" t="n">
-        <v>14417</v>
+        <v>14384</v>
       </c>
       <c r="F96" s="21" t="n">
-        <v>13508</v>
+        <v>12574</v>
       </c>
       <c r="G96" s="21" t="n">
-        <v>12093</v>
+        <v>11681</v>
       </c>
       <c r="H96" s="22" t="n">
-        <v>13996</v>
+        <v>13061</v>
       </c>
       <c r="I96" s="21" t="n">
-        <v>13387</v>
+        <v>12055</v>
       </c>
       <c r="J96" s="22" t="n">
-        <v>13621</v>
+        <v>12325</v>
       </c>
     </row>
     <row r="97">
@@ -6806,25 +6806,25 @@
         <v>24</v>
       </c>
       <c r="D97" s="21" t="n">
-        <v>13657</v>
+        <v>12927</v>
       </c>
       <c r="E97" s="22" t="n">
-        <v>14365</v>
+        <v>14331</v>
       </c>
       <c r="F97" s="21" t="n">
-        <v>13513</v>
+        <v>12632</v>
       </c>
       <c r="G97" s="21" t="n">
-        <v>12738</v>
+        <v>12437</v>
       </c>
       <c r="H97" s="22" t="n">
-        <v>13987</v>
+        <v>13007</v>
       </c>
       <c r="I97" s="21" t="n">
-        <v>13387</v>
+        <v>12019</v>
       </c>
       <c r="J97" s="22" t="n">
-        <v>13830</v>
+        <v>12773</v>
       </c>
     </row>
   </sheetData>
@@ -6989,25 +6989,25 @@
         <v>380.15</v>
       </c>
       <c r="G2" s="23" t="n">
-        <v>352.24</v>
+        <v>335.2</v>
       </c>
       <c r="H2" s="24" t="n">
-        <v>311.81</v>
+        <v>311.03</v>
       </c>
       <c r="I2" s="23" t="n">
-        <v>359.37</v>
+        <v>338.22</v>
       </c>
       <c r="J2" s="23" t="n">
-        <v>370.3</v>
+        <v>364.14</v>
       </c>
       <c r="K2" s="24" t="n">
-        <v>359.92</v>
+        <v>331.85</v>
       </c>
       <c r="L2" s="23" t="n">
-        <v>350.98</v>
+        <v>345.94</v>
       </c>
       <c r="M2" s="24" t="n">
-        <v>357.96</v>
+        <v>318.82</v>
       </c>
     </row>
     <row r="3">
@@ -7030,25 +7030,25 @@
         <v>380.15</v>
       </c>
       <c r="G3" s="23" t="n">
-        <v>352.24</v>
+        <v>333.51</v>
       </c>
       <c r="H3" s="24" t="n">
-        <v>310.22</v>
+        <v>309.36</v>
       </c>
       <c r="I3" s="23" t="n">
-        <v>358.93</v>
+        <v>335.53</v>
       </c>
       <c r="J3" s="23" t="n">
-        <v>370.3</v>
+        <v>358.81</v>
       </c>
       <c r="K3" s="24" t="n">
-        <v>359.72</v>
+        <v>327.1</v>
       </c>
       <c r="L3" s="23" t="n">
-        <v>352.58</v>
+        <v>346.68</v>
       </c>
       <c r="M3" s="24" t="n">
-        <v>358.46</v>
+        <v>322.26</v>
       </c>
     </row>
     <row r="4">
@@ -7071,25 +7071,25 @@
         <v>380.15</v>
       </c>
       <c r="G4" s="23" t="n">
-        <v>346.13</v>
+        <v>326.34</v>
       </c>
       <c r="H4" s="24" t="n">
-        <v>309.29</v>
+        <v>308.33</v>
       </c>
       <c r="I4" s="23" t="n">
-        <v>360.93</v>
+        <v>336.2</v>
       </c>
       <c r="J4" s="23" t="n">
-        <v>366.22</v>
+        <v>358.81</v>
       </c>
       <c r="K4" s="24" t="n">
-        <v>352.08</v>
+        <v>315.98</v>
       </c>
       <c r="L4" s="23" t="n">
-        <v>332.38</v>
+        <v>347.25</v>
       </c>
       <c r="M4" s="24" t="n">
-        <v>353.03</v>
+        <v>290.39</v>
       </c>
     </row>
     <row r="5">
@@ -7112,25 +7112,25 @@
         <v>380.15</v>
       </c>
       <c r="G5" s="23" t="n">
-        <v>333</v>
+        <v>310.04</v>
       </c>
       <c r="H5" s="24" t="n">
-        <v>305.73</v>
+        <v>304.8</v>
       </c>
       <c r="I5" s="23" t="n">
-        <v>347.62</v>
+        <v>319.78</v>
       </c>
       <c r="J5" s="23" t="n">
-        <v>343.21</v>
+        <v>340.24</v>
       </c>
       <c r="K5" s="24" t="n">
-        <v>342.64</v>
+        <v>306.57</v>
       </c>
       <c r="L5" s="23" t="n">
-        <v>318.17</v>
+        <v>309.73</v>
       </c>
       <c r="M5" s="24" t="n">
-        <v>338.29</v>
+        <v>279.14</v>
       </c>
     </row>
     <row r="6">
@@ -7153,25 +7153,25 @@
         <v>600</v>
       </c>
       <c r="G6" s="23" t="n">
-        <v>331.16</v>
+        <v>307.12</v>
       </c>
       <c r="H6" s="24" t="n">
-        <v>304.02</v>
+        <v>303.12</v>
       </c>
       <c r="I6" s="23" t="n">
-        <v>345.22</v>
+        <v>315.56</v>
       </c>
       <c r="J6" s="23" t="n">
-        <v>341.68</v>
+        <v>335.58</v>
       </c>
       <c r="K6" s="24" t="n">
-        <v>342.42</v>
+        <v>305.94</v>
       </c>
       <c r="L6" s="23" t="n">
-        <v>317.36</v>
+        <v>306.92</v>
       </c>
       <c r="M6" s="24" t="n">
-        <v>333.96</v>
+        <v>275.78</v>
       </c>
     </row>
     <row r="7">
@@ -7194,25 +7194,25 @@
         <v>600</v>
       </c>
       <c r="G7" s="23" t="n">
-        <v>321.28</v>
+        <v>292.84</v>
       </c>
       <c r="H7" s="24" t="n">
-        <v>300.35</v>
+        <v>299.48</v>
       </c>
       <c r="I7" s="23" t="n">
-        <v>333.65</v>
+        <v>298.37</v>
       </c>
       <c r="J7" s="23" t="n">
-        <v>336.02</v>
+        <v>331.26</v>
       </c>
       <c r="K7" s="24" t="n">
-        <v>336.45</v>
+        <v>295.33</v>
       </c>
       <c r="L7" s="23" t="n">
-        <v>291.87</v>
+        <v>280.39</v>
       </c>
       <c r="M7" s="24" t="n">
-        <v>327.79</v>
+        <v>253.6</v>
       </c>
     </row>
     <row r="8">
@@ -7235,25 +7235,25 @@
         <v>600</v>
       </c>
       <c r="G8" s="23" t="n">
-        <v>315.07</v>
+        <v>289.6</v>
       </c>
       <c r="H8" s="24" t="n">
-        <v>296.26</v>
+        <v>295.31</v>
       </c>
       <c r="I8" s="23" t="n">
-        <v>334.54</v>
+        <v>291.77</v>
       </c>
       <c r="J8" s="23" t="n">
-        <v>330.82</v>
+        <v>333.04</v>
       </c>
       <c r="K8" s="24" t="n">
-        <v>326.79</v>
+        <v>290.84</v>
       </c>
       <c r="L8" s="23" t="n">
-        <v>291.35</v>
+        <v>279.86</v>
       </c>
       <c r="M8" s="24" t="n">
-        <v>309.16</v>
+        <v>248.31</v>
       </c>
     </row>
     <row r="9">
@@ -7276,25 +7276,25 @@
         <v>600</v>
       </c>
       <c r="G9" s="23" t="n">
-        <v>328.43</v>
+        <v>307.51</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>307.99</v>
+        <v>306.95</v>
       </c>
       <c r="I9" s="23" t="n">
-        <v>342</v>
+        <v>311.75</v>
       </c>
       <c r="J9" s="23" t="n">
-        <v>343.92</v>
+        <v>343.15</v>
       </c>
       <c r="K9" s="24" t="n">
-        <v>341.34</v>
+        <v>307.37</v>
       </c>
       <c r="L9" s="23" t="n">
-        <v>304.93</v>
+        <v>298</v>
       </c>
       <c r="M9" s="24" t="n">
-        <v>328.86</v>
+        <v>278.6</v>
       </c>
     </row>
     <row r="10">
@@ -7317,25 +7317,25 @@
         <v>405</v>
       </c>
       <c r="G10" s="23" t="n">
-        <v>378.44</v>
+        <v>375.5</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>373.39</v>
+        <v>372.01</v>
       </c>
       <c r="I10" s="23" t="n">
-        <v>385.09</v>
+        <v>371.33</v>
       </c>
       <c r="J10" s="23" t="n">
-        <v>382.72</v>
+        <v>378.95</v>
       </c>
       <c r="K10" s="24" t="n">
-        <v>379.92</v>
+        <v>376.32</v>
       </c>
       <c r="L10" s="23" t="n">
-        <v>370.91</v>
+        <v>382.06</v>
       </c>
       <c r="M10" s="24" t="n">
-        <v>378.17</v>
+        <v>372.29</v>
       </c>
     </row>
     <row r="11">
@@ -7358,25 +7358,25 @@
         <v>405</v>
       </c>
       <c r="G11" s="23" t="n">
-        <v>382.32</v>
+        <v>375.6</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>359.52</v>
+        <v>358.68</v>
       </c>
       <c r="I11" s="23" t="n">
-        <v>388.48</v>
+        <v>378.75</v>
       </c>
       <c r="J11" s="23" t="n">
-        <v>382.72</v>
+        <v>378.95</v>
       </c>
       <c r="K11" s="24" t="n">
-        <v>379.67</v>
+        <v>374.21</v>
       </c>
       <c r="L11" s="23" t="n">
-        <v>394.01</v>
+        <v>383.85</v>
       </c>
       <c r="M11" s="24" t="n">
-        <v>387.36</v>
+        <v>377.93</v>
       </c>
     </row>
     <row r="12">
@@ -7399,25 +7399,25 @@
         <v>405</v>
       </c>
       <c r="G12" s="23" t="n">
-        <v>373.61</v>
+        <v>368.6</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>351.07</v>
+        <v>350.28</v>
       </c>
       <c r="I12" s="23" t="n">
-        <v>380.45</v>
+        <v>380.59</v>
       </c>
       <c r="J12" s="23" t="n">
-        <v>382.04</v>
+        <v>379.25</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>371.19</v>
+        <v>363.37</v>
       </c>
       <c r="L12" s="23" t="n">
-        <v>381.76</v>
+        <v>370.97</v>
       </c>
       <c r="M12" s="24" t="n">
-        <v>373.3</v>
+        <v>365.65</v>
       </c>
     </row>
     <row r="13">
@@ -7440,25 +7440,25 @@
         <v>405</v>
       </c>
       <c r="G13" s="23" t="n">
-        <v>370.39</v>
+        <v>364.37</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>351.91</v>
+        <v>351.07</v>
       </c>
       <c r="I13" s="23" t="n">
-        <v>377.46</v>
+        <v>372.55</v>
       </c>
       <c r="J13" s="23" t="n">
-        <v>381.45</v>
+        <v>378.66</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>368</v>
+        <v>358.72</v>
       </c>
       <c r="L13" s="23" t="n">
-        <v>372.74</v>
+        <v>365.77</v>
       </c>
       <c r="M13" s="24" t="n">
-        <v>369.38</v>
+        <v>358.51</v>
       </c>
     </row>
     <row r="14">
@@ -7481,25 +7481,25 @@
         <v>404</v>
       </c>
       <c r="G14" s="23" t="n">
-        <v>370.28</v>
+        <v>363.54</v>
       </c>
       <c r="H14" s="24" t="n">
-        <v>351.42</v>
+        <v>350.55</v>
       </c>
       <c r="I14" s="23" t="n">
-        <v>379.12</v>
+        <v>367.05</v>
       </c>
       <c r="J14" s="23" t="n">
-        <v>382.35</v>
+        <v>379.56</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>368.85</v>
+        <v>359.73</v>
       </c>
       <c r="L14" s="23" t="n">
-        <v>367.4</v>
+        <v>365.07</v>
       </c>
       <c r="M14" s="24" t="n">
-        <v>371.08</v>
+        <v>358.57</v>
       </c>
     </row>
     <row r="15">
@@ -7522,25 +7522,25 @@
         <v>404</v>
       </c>
       <c r="G15" s="23" t="n">
-        <v>369.04</v>
+        <v>361.96</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>343.77</v>
+        <v>342.92</v>
       </c>
       <c r="I15" s="23" t="n">
-        <v>375.16</v>
+        <v>365.09</v>
       </c>
       <c r="J15" s="23" t="n">
-        <v>383.26</v>
+        <v>380.15</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>367.44</v>
+        <v>355.24</v>
       </c>
       <c r="L15" s="23" t="n">
-        <v>369.58</v>
+        <v>365.3</v>
       </c>
       <c r="M15" s="24" t="n">
-        <v>373.1</v>
+        <v>361.9</v>
       </c>
     </row>
     <row r="16">
@@ -7563,25 +7563,25 @@
         <v>404</v>
       </c>
       <c r="G16" s="23" t="n">
-        <v>368.01</v>
+        <v>361.11</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>345.33</v>
+        <v>344.47</v>
       </c>
       <c r="I16" s="23" t="n">
-        <v>376.55</v>
+        <v>367.01</v>
       </c>
       <c r="J16" s="23" t="n">
-        <v>382.67</v>
+        <v>380</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>367.35</v>
+        <v>354.6</v>
       </c>
       <c r="L16" s="23" t="n">
-        <v>365.73</v>
+        <v>362.43</v>
       </c>
       <c r="M16" s="24" t="n">
-        <v>368.74</v>
+        <v>357.11</v>
       </c>
     </row>
     <row r="17">
@@ -7604,25 +7604,25 @@
         <v>404</v>
       </c>
       <c r="G17" s="23" t="n">
-        <v>368.04</v>
+        <v>360.85</v>
       </c>
       <c r="H17" s="24" t="n">
-        <v>346.52</v>
+        <v>345.6</v>
       </c>
       <c r="I17" s="23" t="n">
-        <v>376.39</v>
+        <v>364.39</v>
       </c>
       <c r="J17" s="23" t="n">
-        <v>382.67</v>
+        <v>380</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>367.27</v>
+        <v>354.99</v>
       </c>
       <c r="L17" s="23" t="n">
-        <v>365.56</v>
+        <v>361.43</v>
       </c>
       <c r="M17" s="24" t="n">
-        <v>368.28</v>
+        <v>357.85</v>
       </c>
     </row>
     <row r="18">
@@ -7645,25 +7645,25 @@
         <v>493</v>
       </c>
       <c r="G18" s="23" t="n">
-        <v>366.11</v>
+        <v>360.93</v>
       </c>
       <c r="H18" s="24" t="n">
-        <v>347.22</v>
+        <v>346.29</v>
       </c>
       <c r="I18" s="23" t="n">
-        <v>374.45</v>
+        <v>363.27</v>
       </c>
       <c r="J18" s="23" t="n">
-        <v>382.67</v>
+        <v>380</v>
       </c>
       <c r="K18" s="24" t="n">
-        <v>367.53</v>
+        <v>356.93</v>
       </c>
       <c r="L18" s="23" t="n">
-        <v>364.79</v>
+        <v>361.13</v>
       </c>
       <c r="M18" s="24" t="n">
-        <v>358.75</v>
+        <v>357.21</v>
       </c>
     </row>
     <row r="19">
@@ -7686,25 +7686,25 @@
         <v>493</v>
       </c>
       <c r="G19" s="23" t="n">
-        <v>367.79</v>
+        <v>363.89</v>
       </c>
       <c r="H19" s="24" t="n">
-        <v>351.18</v>
+        <v>350.17</v>
       </c>
       <c r="I19" s="23" t="n">
-        <v>375.5</v>
+        <v>366.41</v>
       </c>
       <c r="J19" s="23" t="n">
-        <v>382.67</v>
+        <v>380</v>
       </c>
       <c r="K19" s="24" t="n">
-        <v>368.92</v>
+        <v>359.45</v>
       </c>
       <c r="L19" s="23" t="n">
-        <v>365.51</v>
+        <v>366.07</v>
       </c>
       <c r="M19" s="24" t="n">
-        <v>361.82</v>
+        <v>360.49</v>
       </c>
     </row>
     <row r="20">
@@ -7727,25 +7727,25 @@
         <v>493</v>
       </c>
       <c r="G20" s="23" t="n">
-        <v>367.92</v>
+        <v>363.87</v>
       </c>
       <c r="H20" s="24" t="n">
-        <v>351.95</v>
+        <v>350.94</v>
       </c>
       <c r="I20" s="23" t="n">
-        <v>379.05</v>
+        <v>367.73</v>
       </c>
       <c r="J20" s="23" t="n">
-        <v>380.5</v>
+        <v>380</v>
       </c>
       <c r="K20" s="24" t="n">
-        <v>369.1</v>
+        <v>360.23</v>
       </c>
       <c r="L20" s="23" t="n">
-        <v>365.73</v>
+        <v>365.74</v>
       </c>
       <c r="M20" s="24" t="n">
-        <v>359.96</v>
+        <v>357.87</v>
       </c>
     </row>
     <row r="21">
@@ -7768,25 +7768,25 @@
         <v>493</v>
       </c>
       <c r="G21" s="23" t="n">
-        <v>371.92</v>
+        <v>370.22</v>
       </c>
       <c r="H21" s="24" t="n">
-        <v>357.56</v>
+        <v>356.53</v>
       </c>
       <c r="I21" s="23" t="n">
-        <v>381.83</v>
+        <v>374.23</v>
       </c>
       <c r="J21" s="23" t="n">
-        <v>380.18</v>
+        <v>380.29</v>
       </c>
       <c r="K21" s="24" t="n">
-        <v>377.86</v>
+        <v>368.23</v>
       </c>
       <c r="L21" s="23" t="n">
-        <v>369.41</v>
+        <v>374.68</v>
       </c>
       <c r="M21" s="24" t="n">
-        <v>363.5</v>
+        <v>366.44</v>
       </c>
     </row>
     <row r="22">
@@ -7809,25 +7809,25 @@
         <v>495</v>
       </c>
       <c r="G22" s="23" t="n">
-        <v>378.5</v>
+        <v>376.44</v>
       </c>
       <c r="H22" s="24" t="n">
-        <v>363.94</v>
+        <v>362.93</v>
       </c>
       <c r="I22" s="23" t="n">
-        <v>391.31</v>
+        <v>386.81</v>
       </c>
       <c r="J22" s="23" t="n">
-        <v>380.18</v>
+        <v>380.29</v>
       </c>
       <c r="K22" s="24" t="n">
-        <v>383.06</v>
+        <v>376.14</v>
       </c>
       <c r="L22" s="23" t="n">
-        <v>380.47</v>
+        <v>381.41</v>
       </c>
       <c r="M22" s="24" t="n">
-        <v>370.59</v>
+        <v>369.91</v>
       </c>
     </row>
     <row r="23">
@@ -7850,25 +7850,25 @@
         <v>495</v>
       </c>
       <c r="G23" s="23" t="n">
-        <v>380.77</v>
+        <v>378.37</v>
       </c>
       <c r="H23" s="24" t="n">
-        <v>368.39</v>
+        <v>367.37</v>
       </c>
       <c r="I23" s="23" t="n">
-        <v>388.88</v>
+        <v>384.94</v>
       </c>
       <c r="J23" s="23" t="n">
-        <v>380.49</v>
+        <v>380.29</v>
       </c>
       <c r="K23" s="24" t="n">
-        <v>384.28</v>
+        <v>377.55</v>
       </c>
       <c r="L23" s="23" t="n">
-        <v>384.69</v>
+        <v>383.05</v>
       </c>
       <c r="M23" s="24" t="n">
-        <v>376.66</v>
+        <v>376.07</v>
       </c>
     </row>
     <row r="24">
@@ -7891,25 +7891,25 @@
         <v>495</v>
       </c>
       <c r="G24" s="23" t="n">
-        <v>382.72</v>
+        <v>380.84</v>
       </c>
       <c r="H24" s="24" t="n">
-        <v>378.27</v>
+        <v>377.31</v>
       </c>
       <c r="I24" s="23" t="n">
-        <v>391.02</v>
+        <v>388.31</v>
       </c>
       <c r="J24" s="23" t="n">
-        <v>380.36</v>
+        <v>381.19</v>
       </c>
       <c r="K24" s="24" t="n">
-        <v>385.5</v>
+        <v>377.88</v>
       </c>
       <c r="L24" s="23" t="n">
-        <v>383.92</v>
+        <v>383.46</v>
       </c>
       <c r="M24" s="24" t="n">
-        <v>376.62</v>
+        <v>376.32</v>
       </c>
     </row>
     <row r="25">
@@ -7932,25 +7932,25 @@
         <v>495</v>
       </c>
       <c r="G25" s="23" t="n">
-        <v>388.75</v>
+        <v>387.16</v>
       </c>
       <c r="H25" s="24" t="n">
-        <v>391.97</v>
+        <v>390.86</v>
       </c>
       <c r="I25" s="23" t="n">
-        <v>402.09</v>
+        <v>397.33</v>
       </c>
       <c r="J25" s="23" t="n">
-        <v>384.99</v>
+        <v>384.43</v>
       </c>
       <c r="K25" s="24" t="n">
-        <v>388.82</v>
+        <v>384.4</v>
       </c>
       <c r="L25" s="23" t="n">
-        <v>385.94</v>
+        <v>384.57</v>
       </c>
       <c r="M25" s="24" t="n">
-        <v>378.62</v>
+        <v>381.23</v>
       </c>
     </row>
     <row r="26">
@@ -7973,25 +7973,25 @@
         <v>426</v>
       </c>
       <c r="G26" s="23" t="n">
-        <v>397.19</v>
+        <v>395.74</v>
       </c>
       <c r="H26" s="24" t="n">
-        <v>406.56</v>
+        <v>405.14</v>
       </c>
       <c r="I26" s="23" t="n">
-        <v>405.99</v>
+        <v>400.59</v>
       </c>
       <c r="J26" s="23" t="n">
-        <v>389.89</v>
+        <v>390.13</v>
       </c>
       <c r="K26" s="24" t="n">
-        <v>392.85</v>
+        <v>389.55</v>
       </c>
       <c r="L26" s="23" t="n">
-        <v>399.13</v>
+        <v>399.1</v>
       </c>
       <c r="M26" s="24" t="n">
-        <v>389.11</v>
+        <v>390.18</v>
       </c>
     </row>
     <row r="27">
@@ -8014,25 +8014,25 @@
         <v>426</v>
       </c>
       <c r="G27" s="23" t="n">
-        <v>412.86</v>
+        <v>410.84</v>
       </c>
       <c r="H27" s="24" t="n">
-        <v>434.23</v>
+        <v>432.66</v>
       </c>
       <c r="I27" s="23" t="n">
-        <v>415.43</v>
+        <v>416.97</v>
       </c>
       <c r="J27" s="23" t="n">
-        <v>399.04</v>
+        <v>399.46</v>
       </c>
       <c r="K27" s="24" t="n">
-        <v>402.89</v>
+        <v>400.91</v>
       </c>
       <c r="L27" s="23" t="n">
-        <v>420.86</v>
+        <v>417.14</v>
       </c>
       <c r="M27" s="24" t="n">
-        <v>406.07</v>
+        <v>398.7</v>
       </c>
     </row>
     <row r="28">
@@ -8055,25 +8055,25 @@
         <v>426</v>
       </c>
       <c r="G28" s="23" t="n">
-        <v>422.51</v>
+        <v>423.68</v>
       </c>
       <c r="H28" s="24" t="n">
-        <v>450.55</v>
+        <v>448.9</v>
       </c>
       <c r="I28" s="23" t="n">
-        <v>420.13</v>
+        <v>428.3</v>
       </c>
       <c r="J28" s="23" t="n">
-        <v>417.54</v>
+        <v>417.6</v>
       </c>
       <c r="K28" s="24" t="n">
-        <v>411.12</v>
+        <v>408.97</v>
       </c>
       <c r="L28" s="23" t="n">
-        <v>423.09</v>
+        <v>424.29</v>
       </c>
       <c r="M28" s="24" t="n">
-        <v>414.99</v>
+        <v>415.13</v>
       </c>
     </row>
     <row r="29">
@@ -8096,25 +8096,25 @@
         <v>426</v>
       </c>
       <c r="G29" s="23" t="n">
-        <v>424.73</v>
+        <v>427.07</v>
       </c>
       <c r="H29" s="24" t="n">
-        <v>465.1</v>
+        <v>463.43</v>
       </c>
       <c r="I29" s="23" t="n">
-        <v>414.86</v>
+        <v>425.27</v>
       </c>
       <c r="J29" s="23" t="n">
-        <v>421.76</v>
+        <v>421.06</v>
       </c>
       <c r="K29" s="24" t="n">
-        <v>412.03</v>
+        <v>410.59</v>
       </c>
       <c r="L29" s="23" t="n">
-        <v>422.83</v>
+        <v>428.08</v>
       </c>
       <c r="M29" s="24" t="n">
-        <v>415.43</v>
+        <v>416.04</v>
       </c>
     </row>
     <row r="30">
@@ -8137,25 +8137,25 @@
         <v>433.96</v>
       </c>
       <c r="G30" s="23" t="n">
-        <v>427.57</v>
+        <v>426.6</v>
       </c>
       <c r="H30" s="24" t="n">
-        <v>471.81</v>
+        <v>470.22</v>
       </c>
       <c r="I30" s="23" t="n">
-        <v>419.18</v>
+        <v>418.91</v>
       </c>
       <c r="J30" s="23" t="n">
-        <v>422.12</v>
+        <v>421.06</v>
       </c>
       <c r="K30" s="24" t="n">
-        <v>410.85</v>
+        <v>409.18</v>
       </c>
       <c r="L30" s="23" t="n">
-        <v>424.62</v>
+        <v>426.07</v>
       </c>
       <c r="M30" s="24" t="n">
-        <v>420.7</v>
+        <v>416.89</v>
       </c>
     </row>
     <row r="31">
@@ -8178,25 +8178,25 @@
         <v>433.96</v>
       </c>
       <c r="G31" s="23" t="n">
-        <v>423.5</v>
+        <v>424.01</v>
       </c>
       <c r="H31" s="24" t="n">
-        <v>467.96</v>
+        <v>466.48</v>
       </c>
       <c r="I31" s="23" t="n">
-        <v>412.2</v>
+        <v>421.24</v>
       </c>
       <c r="J31" s="23" t="n">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="K31" s="24" t="n">
-        <v>408.66</v>
+        <v>404.66</v>
       </c>
       <c r="L31" s="23" t="n">
-        <v>423.23</v>
+        <v>424.03</v>
       </c>
       <c r="M31" s="24" t="n">
-        <v>411</v>
+        <v>410.16</v>
       </c>
     </row>
     <row r="32">
@@ -8219,25 +8219,25 @@
         <v>433.96</v>
       </c>
       <c r="G32" s="23" t="n">
-        <v>423.04</v>
+        <v>420.7</v>
       </c>
       <c r="H32" s="24" t="n">
-        <v>472.89</v>
+        <v>471.47</v>
       </c>
       <c r="I32" s="23" t="n">
-        <v>417.71</v>
+        <v>412.89</v>
       </c>
       <c r="J32" s="23" t="n">
-        <v>420.92</v>
+        <v>418.61</v>
       </c>
       <c r="K32" s="24" t="n">
-        <v>406.85</v>
+        <v>403.74</v>
       </c>
       <c r="L32" s="23" t="n">
-        <v>418.52</v>
+        <v>416.94</v>
       </c>
       <c r="M32" s="24" t="n">
-        <v>405.76</v>
+        <v>403.88</v>
       </c>
     </row>
     <row r="33">
@@ -8260,25 +8260,25 @@
         <v>433.96</v>
       </c>
       <c r="G33" s="23" t="n">
-        <v>424.49</v>
+        <v>423.22</v>
       </c>
       <c r="H33" s="24" t="n">
-        <v>479.22</v>
+        <v>477.89</v>
       </c>
       <c r="I33" s="23" t="n">
-        <v>417.53</v>
+        <v>412.69</v>
       </c>
       <c r="J33" s="23" t="n">
-        <v>420.92</v>
+        <v>419.57</v>
       </c>
       <c r="K33" s="24" t="n">
-        <v>406.25</v>
+        <v>403.83</v>
       </c>
       <c r="L33" s="23" t="n">
-        <v>420.45</v>
+        <v>420.78</v>
       </c>
       <c r="M33" s="24" t="n">
-        <v>407.41</v>
+        <v>408.14</v>
       </c>
     </row>
     <row r="34">
@@ -8301,25 +8301,25 @@
         <v>399</v>
       </c>
       <c r="G34" s="23" t="n">
-        <v>436.69</v>
+        <v>430.83</v>
       </c>
       <c r="H34" s="24" t="n">
-        <v>489.86</v>
+        <v>488.59</v>
       </c>
       <c r="I34" s="23" t="n">
-        <v>416.38</v>
+        <v>412.34</v>
       </c>
       <c r="J34" s="23" t="n">
-        <v>439.93</v>
+        <v>425.25</v>
       </c>
       <c r="K34" s="24" t="n">
-        <v>411.59</v>
+        <v>407.51</v>
       </c>
       <c r="L34" s="23" t="n">
-        <v>449.67</v>
+        <v>433.67</v>
       </c>
       <c r="M34" s="24" t="n">
-        <v>417.87</v>
+        <v>421.45</v>
       </c>
     </row>
     <row r="35">
@@ -8342,25 +8342,25 @@
         <v>399</v>
       </c>
       <c r="G35" s="23" t="n">
-        <v>427.29</v>
+        <v>426.24</v>
       </c>
       <c r="H35" s="24" t="n">
-        <v>489.23</v>
+        <v>488.22</v>
       </c>
       <c r="I35" s="23" t="n">
-        <v>401.15</v>
+        <v>404.16</v>
       </c>
       <c r="J35" s="23" t="n">
-        <v>412.28</v>
+        <v>417.75</v>
       </c>
       <c r="K35" s="24" t="n">
-        <v>406.12</v>
+        <v>402.22</v>
       </c>
       <c r="L35" s="23" t="n">
-        <v>440.27</v>
+        <v>428.26</v>
       </c>
       <c r="M35" s="24" t="n">
-        <v>420.13</v>
+        <v>421.02</v>
       </c>
     </row>
     <row r="36">
@@ -8383,25 +8383,25 @@
         <v>399</v>
       </c>
       <c r="G36" s="23" t="n">
-        <v>423.87</v>
+        <v>423.83</v>
       </c>
       <c r="H36" s="24" t="n">
-        <v>481.1</v>
+        <v>480.25</v>
       </c>
       <c r="I36" s="23" t="n">
-        <v>400.39</v>
+        <v>402.88</v>
       </c>
       <c r="J36" s="23" t="n">
-        <v>412.28</v>
+        <v>416.33</v>
       </c>
       <c r="K36" s="24" t="n">
-        <v>404.35</v>
+        <v>401.16</v>
       </c>
       <c r="L36" s="23" t="n">
-        <v>434.78</v>
+        <v>429.66</v>
       </c>
       <c r="M36" s="24" t="n">
-        <v>415.39</v>
+        <v>416.47</v>
       </c>
     </row>
     <row r="37">
@@ -8424,25 +8424,25 @@
         <v>399</v>
       </c>
       <c r="G37" s="23" t="n">
-        <v>415.79</v>
+        <v>414.07</v>
       </c>
       <c r="H37" s="24" t="n">
-        <v>474.15</v>
+        <v>473.43</v>
       </c>
       <c r="I37" s="23" t="n">
-        <v>397.16</v>
+        <v>387.22</v>
       </c>
       <c r="J37" s="23" t="n">
-        <v>409.28</v>
+        <v>413.18</v>
       </c>
       <c r="K37" s="24" t="n">
-        <v>399.36</v>
+        <v>395.73</v>
       </c>
       <c r="L37" s="23" t="n">
-        <v>412.65</v>
+        <v>410.21</v>
       </c>
       <c r="M37" s="24" t="n">
-        <v>407.38</v>
+        <v>409.11</v>
       </c>
     </row>
     <row r="38">
@@ -8465,25 +8465,25 @@
         <v>310.01</v>
       </c>
       <c r="G38" s="23" t="n">
-        <v>408.74</v>
+        <v>409.38</v>
       </c>
       <c r="H38" s="24" t="n">
-        <v>465.04</v>
+        <v>464.41</v>
       </c>
       <c r="I38" s="23" t="n">
-        <v>379.58</v>
+        <v>384.31</v>
       </c>
       <c r="J38" s="23" t="n">
-        <v>408.12</v>
+        <v>411.57</v>
       </c>
       <c r="K38" s="24" t="n">
-        <v>396.31</v>
+        <v>391.73</v>
       </c>
       <c r="L38" s="23" t="n">
-        <v>405.34</v>
+        <v>407</v>
       </c>
       <c r="M38" s="24" t="n">
-        <v>403.55</v>
+        <v>401.45</v>
       </c>
     </row>
     <row r="39">
@@ -8506,25 +8506,25 @@
         <v>310.01</v>
       </c>
       <c r="G39" s="23" t="n">
-        <v>408.38</v>
+        <v>407.24</v>
       </c>
       <c r="H39" s="24" t="n">
-        <v>466.37</v>
+        <v>465.64</v>
       </c>
       <c r="I39" s="23" t="n">
-        <v>374.97</v>
+        <v>375.39</v>
       </c>
       <c r="J39" s="23" t="n">
-        <v>408.32</v>
+        <v>410.49</v>
       </c>
       <c r="K39" s="24" t="n">
-        <v>395.72</v>
+        <v>390.79</v>
       </c>
       <c r="L39" s="23" t="n">
-        <v>406.17</v>
+        <v>403.91</v>
       </c>
       <c r="M39" s="24" t="n">
-        <v>404.49</v>
+        <v>401.9</v>
       </c>
     </row>
     <row r="40">
@@ -8547,25 +8547,25 @@
         <v>310.01</v>
       </c>
       <c r="G40" s="23" t="n">
-        <v>403.03</v>
+        <v>403.29</v>
       </c>
       <c r="H40" s="24" t="n">
-        <v>454.46</v>
+        <v>453.77</v>
       </c>
       <c r="I40" s="23" t="n">
-        <v>373.42</v>
+        <v>377.64</v>
       </c>
       <c r="J40" s="23" t="n">
-        <v>404.83</v>
+        <v>408.78</v>
       </c>
       <c r="K40" s="24" t="n">
-        <v>391.32</v>
+        <v>387.02</v>
       </c>
       <c r="L40" s="23" t="n">
-        <v>400.6</v>
+        <v>400.11</v>
       </c>
       <c r="M40" s="24" t="n">
-        <v>398.71</v>
+        <v>396.44</v>
       </c>
     </row>
     <row r="41">
@@ -8588,25 +8588,25 @@
         <v>310.01</v>
       </c>
       <c r="G41" s="23" t="n">
-        <v>398.52</v>
+        <v>398.31</v>
       </c>
       <c r="H41" s="24" t="n">
-        <v>441.78</v>
+        <v>440.99</v>
       </c>
       <c r="I41" s="23" t="n">
-        <v>372.58</v>
+        <v>373.07</v>
       </c>
       <c r="J41" s="23" t="n">
-        <v>404.02</v>
+        <v>407.12</v>
       </c>
       <c r="K41" s="24" t="n">
-        <v>387.92</v>
+        <v>383.61</v>
       </c>
       <c r="L41" s="23" t="n">
-        <v>396.88</v>
+        <v>396.84</v>
       </c>
       <c r="M41" s="24" t="n">
-        <v>392.41</v>
+        <v>391.8</v>
       </c>
     </row>
     <row r="42">
@@ -8629,25 +8629,25 @@
         <v>272</v>
       </c>
       <c r="G42" s="23" t="n">
-        <v>397.34</v>
+        <v>396.59</v>
       </c>
       <c r="H42" s="24" t="n">
-        <v>433.49</v>
+        <v>432.55</v>
       </c>
       <c r="I42" s="23" t="n">
-        <v>376.05</v>
+        <v>377.03</v>
       </c>
       <c r="J42" s="23" t="n">
-        <v>402.09</v>
+        <v>405.27</v>
       </c>
       <c r="K42" s="24" t="n">
-        <v>386.13</v>
+        <v>383.12</v>
       </c>
       <c r="L42" s="23" t="n">
-        <v>392.72</v>
+        <v>390.77</v>
       </c>
       <c r="M42" s="24" t="n">
-        <v>397.3</v>
+        <v>393.73</v>
       </c>
     </row>
     <row r="43">
@@ -8670,25 +8670,25 @@
         <v>272</v>
       </c>
       <c r="G43" s="23" t="n">
-        <v>391.66</v>
+        <v>392.03</v>
       </c>
       <c r="H43" s="24" t="n">
-        <v>420.7</v>
+        <v>419.75</v>
       </c>
       <c r="I43" s="23" t="n">
-        <v>371.19</v>
+        <v>373.47</v>
       </c>
       <c r="J43" s="23" t="n">
-        <v>396.79</v>
+        <v>400.3</v>
       </c>
       <c r="K43" s="24" t="n">
-        <v>384.76</v>
+        <v>379.6</v>
       </c>
       <c r="L43" s="23" t="n">
-        <v>388.23</v>
+        <v>390.83</v>
       </c>
       <c r="M43" s="24" t="n">
-        <v>391.42</v>
+        <v>390.62</v>
       </c>
     </row>
     <row r="44">
@@ -8711,25 +8711,25 @@
         <v>272</v>
       </c>
       <c r="G44" s="23" t="n">
-        <v>381.77</v>
+        <v>381.2</v>
       </c>
       <c r="H44" s="24" t="n">
-        <v>407.43</v>
+        <v>406.43</v>
       </c>
       <c r="I44" s="23" t="n">
-        <v>370.17</v>
+        <v>370.46</v>
       </c>
       <c r="J44" s="23" t="n">
-        <v>376.56</v>
+        <v>378.35</v>
       </c>
       <c r="K44" s="24" t="n">
-        <v>380.07</v>
+        <v>375.13</v>
       </c>
       <c r="L44" s="23" t="n">
-        <v>377.45</v>
+        <v>378.26</v>
       </c>
       <c r="M44" s="24" t="n">
-        <v>381.24</v>
+        <v>380.43</v>
       </c>
     </row>
     <row r="45">
@@ -8752,25 +8752,25 @@
         <v>272</v>
       </c>
       <c r="G45" s="23" t="n">
-        <v>376.15</v>
+        <v>375.83</v>
       </c>
       <c r="H45" s="24" t="n">
-        <v>396.02</v>
+        <v>395.09</v>
       </c>
       <c r="I45" s="23" t="n">
-        <v>364.44</v>
+        <v>370.33</v>
       </c>
       <c r="J45" s="23" t="n">
-        <v>370.77</v>
+        <v>373.22</v>
       </c>
       <c r="K45" s="24" t="n">
-        <v>373.47</v>
+        <v>367.9</v>
       </c>
       <c r="L45" s="23" t="n">
-        <v>376.76</v>
+        <v>375.45</v>
       </c>
       <c r="M45" s="24" t="n">
-        <v>377.25</v>
+        <v>374.24</v>
       </c>
     </row>
     <row r="46">
@@ -8793,25 +8793,25 @@
         <v>273.92</v>
       </c>
       <c r="G46" s="23" t="n">
-        <v>392.45</v>
+        <v>384.6</v>
       </c>
       <c r="H46" s="24" t="n">
-        <v>427.91</v>
+        <v>426.73</v>
       </c>
       <c r="I46" s="23" t="n">
-        <v>372.46</v>
+        <v>366.27</v>
       </c>
       <c r="J46" s="23" t="n">
-        <v>381.37</v>
+        <v>386.19</v>
       </c>
       <c r="K46" s="24" t="n">
-        <v>391.84</v>
+        <v>381.18</v>
       </c>
       <c r="L46" s="23" t="n">
-        <v>392.35</v>
+        <v>369.53</v>
       </c>
       <c r="M46" s="24" t="n">
-        <v>391.93</v>
+        <v>381.2</v>
       </c>
     </row>
     <row r="47">
@@ -8834,25 +8834,25 @@
         <v>273.92</v>
       </c>
       <c r="G47" s="23" t="n">
-        <v>398.19</v>
+        <v>390.17</v>
       </c>
       <c r="H47" s="24" t="n">
-        <v>413.8</v>
+        <v>412.77</v>
       </c>
       <c r="I47" s="23" t="n">
-        <v>381.18</v>
+        <v>378.31</v>
       </c>
       <c r="J47" s="23" t="n">
-        <v>381.56</v>
+        <v>384.8</v>
       </c>
       <c r="K47" s="24" t="n">
-        <v>389.68</v>
+        <v>379.53</v>
       </c>
       <c r="L47" s="23" t="n">
-        <v>411.37</v>
+        <v>392.05</v>
       </c>
       <c r="M47" s="24" t="n">
-        <v>412.67</v>
+        <v>395.11</v>
       </c>
     </row>
     <row r="48">
@@ -8875,25 +8875,25 @@
         <v>273.92</v>
       </c>
       <c r="G48" s="23" t="n">
-        <v>388.11</v>
+        <v>378.69</v>
       </c>
       <c r="H48" s="24" t="n">
-        <v>388.74</v>
+        <v>387.7</v>
       </c>
       <c r="I48" s="23" t="n">
-        <v>383.57</v>
+        <v>367.51</v>
       </c>
       <c r="J48" s="23" t="n">
-        <v>380.9</v>
+        <v>384.03</v>
       </c>
       <c r="K48" s="24" t="n">
-        <v>382.17</v>
+        <v>370.64</v>
       </c>
       <c r="L48" s="23" t="n">
-        <v>394.83</v>
+        <v>377.15</v>
       </c>
       <c r="M48" s="24" t="n">
-        <v>398.35</v>
+        <v>386.01</v>
       </c>
     </row>
     <row r="49">
@@ -8916,25 +8916,25 @@
         <v>273.92</v>
       </c>
       <c r="G49" s="23" t="n">
-        <v>349.39</v>
+        <v>344.57</v>
       </c>
       <c r="H49" s="24" t="n">
-        <v>347.32</v>
+        <v>346.81</v>
       </c>
       <c r="I49" s="23" t="n">
-        <v>350.73</v>
+        <v>359.18</v>
       </c>
       <c r="J49" s="23" t="n">
-        <v>366.49</v>
+        <v>366.94</v>
       </c>
       <c r="K49" s="24" t="n">
-        <v>358.51</v>
+        <v>347.33</v>
       </c>
       <c r="L49" s="23" t="n">
-        <v>325.72</v>
+        <v>316.82</v>
       </c>
       <c r="M49" s="24" t="n">
-        <v>347.95</v>
+        <v>330.81</v>
       </c>
     </row>
     <row r="50">
@@ -8957,25 +8957,25 @@
         <v>273.29</v>
       </c>
       <c r="G50" s="23" t="n">
-        <v>355.97</v>
+        <v>342.37</v>
       </c>
       <c r="H50" s="24" t="n">
-        <v>342.5</v>
+        <v>341.8</v>
       </c>
       <c r="I50" s="23" t="n">
-        <v>360.11</v>
+        <v>340.29</v>
       </c>
       <c r="J50" s="23" t="n">
-        <v>367.57</v>
+        <v>369.57</v>
       </c>
       <c r="K50" s="24" t="n">
-        <v>358.43</v>
+        <v>330.56</v>
       </c>
       <c r="L50" s="23" t="n">
-        <v>346.8</v>
+        <v>335.18</v>
       </c>
       <c r="M50" s="24" t="n">
-        <v>359.5</v>
+        <v>337.26</v>
       </c>
     </row>
     <row r="51">
@@ -8998,25 +8998,25 @@
         <v>273.29</v>
       </c>
       <c r="G51" s="23" t="n">
-        <v>345.65</v>
+        <v>331.31</v>
       </c>
       <c r="H51" s="24" t="n">
-        <v>322.91</v>
+        <v>322.46</v>
       </c>
       <c r="I51" s="23" t="n">
-        <v>347.8</v>
+        <v>330.82</v>
       </c>
       <c r="J51" s="23" t="n">
-        <v>367.89</v>
+        <v>365.65</v>
       </c>
       <c r="K51" s="24" t="n">
-        <v>349</v>
+        <v>322.94</v>
       </c>
       <c r="L51" s="23" t="n">
-        <v>334.52</v>
+        <v>322.73</v>
       </c>
       <c r="M51" s="24" t="n">
-        <v>350.5</v>
+        <v>323.33</v>
       </c>
     </row>
     <row r="52">
@@ -9039,25 +9039,25 @@
         <v>273.29</v>
       </c>
       <c r="G52" s="23" t="n">
-        <v>326.24</v>
+        <v>299.21</v>
       </c>
       <c r="H52" s="24" t="n">
-        <v>313.31</v>
+        <v>312.85</v>
       </c>
       <c r="I52" s="23" t="n">
-        <v>324.33</v>
+        <v>272.09</v>
       </c>
       <c r="J52" s="23" t="n">
-        <v>342.52</v>
+        <v>338.01</v>
       </c>
       <c r="K52" s="24" t="n">
-        <v>340.9</v>
+        <v>300.41</v>
       </c>
       <c r="L52" s="23" t="n">
-        <v>301.85</v>
+        <v>272.38</v>
       </c>
       <c r="M52" s="24" t="n">
-        <v>334.02</v>
+        <v>302.29</v>
       </c>
     </row>
     <row r="53">
@@ -9080,25 +9080,25 @@
         <v>273.29</v>
       </c>
       <c r="G53" s="23" t="n">
-        <v>324.14</v>
+        <v>294.69</v>
       </c>
       <c r="H53" s="24" t="n">
-        <v>313.04</v>
+        <v>312.54</v>
       </c>
       <c r="I53" s="23" t="n">
-        <v>321.94</v>
+        <v>260</v>
       </c>
       <c r="J53" s="23" t="n">
-        <v>342.61</v>
+        <v>340.36</v>
       </c>
       <c r="K53" s="24" t="n">
-        <v>337.58</v>
+        <v>294.66</v>
       </c>
       <c r="L53" s="23" t="n">
-        <v>300.05</v>
+        <v>268.43</v>
       </c>
       <c r="M53" s="24" t="n">
-        <v>329.32</v>
+        <v>295.6</v>
       </c>
     </row>
     <row r="54">
@@ -9121,25 +9121,25 @@
         <v>300.01</v>
       </c>
       <c r="G54" s="23" t="n">
-        <v>339.29</v>
+        <v>318.53</v>
       </c>
       <c r="H54" s="24" t="n">
-        <v>322.94</v>
+        <v>322.32</v>
       </c>
       <c r="I54" s="23" t="n">
-        <v>346.48</v>
+        <v>300.55</v>
       </c>
       <c r="J54" s="23" t="n">
-        <v>364.81</v>
+        <v>360.47</v>
       </c>
       <c r="K54" s="24" t="n">
-        <v>341.62</v>
+        <v>313.53</v>
       </c>
       <c r="L54" s="23" t="n">
-        <v>315.29</v>
+        <v>303.32</v>
       </c>
       <c r="M54" s="24" t="n">
-        <v>343.85</v>
+        <v>312.73</v>
       </c>
     </row>
     <row r="55">
@@ -9162,25 +9162,25 @@
         <v>300.01</v>
       </c>
       <c r="G55" s="23" t="n">
-        <v>341.54</v>
+        <v>324.55</v>
       </c>
       <c r="H55" s="24" t="n">
-        <v>329.22</v>
+        <v>328.49</v>
       </c>
       <c r="I55" s="23" t="n">
-        <v>352.83</v>
+        <v>316.04</v>
       </c>
       <c r="J55" s="23" t="n">
-        <v>367.19</v>
+        <v>362.4</v>
       </c>
       <c r="K55" s="24" t="n">
-        <v>343.34</v>
+        <v>319.58</v>
       </c>
       <c r="L55" s="23" t="n">
-        <v>312.7</v>
+        <v>307.3</v>
       </c>
       <c r="M55" s="24" t="n">
-        <v>343.53</v>
+        <v>314.9</v>
       </c>
     </row>
     <row r="56">
@@ -9203,25 +9203,25 @@
         <v>300.01</v>
       </c>
       <c r="G56" s="23" t="n">
-        <v>344.58</v>
+        <v>326.96</v>
       </c>
       <c r="H56" s="24" t="n">
-        <v>334.48</v>
+        <v>333.75</v>
       </c>
       <c r="I56" s="23" t="n">
-        <v>351.71</v>
+        <v>311.89</v>
       </c>
       <c r="J56" s="23" t="n">
-        <v>368.49</v>
+        <v>365.57</v>
       </c>
       <c r="K56" s="24" t="n">
-        <v>345.15</v>
+        <v>321.87</v>
       </c>
       <c r="L56" s="23" t="n">
-        <v>321.33</v>
+        <v>310.44</v>
       </c>
       <c r="M56" s="24" t="n">
-        <v>346.12</v>
+        <v>320.04</v>
       </c>
     </row>
     <row r="57">
@@ -9244,25 +9244,25 @@
         <v>300.01</v>
       </c>
       <c r="G57" s="23" t="n">
-        <v>346.76</v>
+        <v>328.73</v>
       </c>
       <c r="H57" s="24" t="n">
-        <v>340.85</v>
+        <v>340.06</v>
       </c>
       <c r="I57" s="23" t="n">
-        <v>355.65</v>
+        <v>314.39</v>
       </c>
       <c r="J57" s="23" t="n">
-        <v>368.49</v>
+        <v>365.75</v>
       </c>
       <c r="K57" s="24" t="n">
-        <v>346.7</v>
+        <v>322.64</v>
       </c>
       <c r="L57" s="23" t="n">
-        <v>323.2</v>
+        <v>310.95</v>
       </c>
       <c r="M57" s="24" t="n">
-        <v>345.68</v>
+        <v>320.61</v>
       </c>
     </row>
     <row r="58">
@@ -9285,25 +9285,25 @@
         <v>334.39</v>
       </c>
       <c r="G58" s="23" t="n">
-        <v>345.29</v>
+        <v>330.81</v>
       </c>
       <c r="H58" s="24" t="n">
-        <v>345.87</v>
+        <v>345.1</v>
       </c>
       <c r="I58" s="23" t="n">
-        <v>343.69</v>
+        <v>317.09</v>
       </c>
       <c r="J58" s="23" t="n">
-        <v>368.49</v>
+        <v>369.14</v>
       </c>
       <c r="K58" s="24" t="n">
-        <v>346.57</v>
+        <v>325.5</v>
       </c>
       <c r="L58" s="23" t="n">
-        <v>321.81</v>
+        <v>311.85</v>
       </c>
       <c r="M58" s="24" t="n">
-        <v>346.15</v>
+        <v>318.48</v>
       </c>
     </row>
     <row r="59">
@@ -9326,25 +9326,25 @@
         <v>334.39</v>
       </c>
       <c r="G59" s="23" t="n">
-        <v>352.94</v>
+        <v>341.26</v>
       </c>
       <c r="H59" s="24" t="n">
-        <v>355.91</v>
+        <v>355.12</v>
       </c>
       <c r="I59" s="23" t="n">
-        <v>354.16</v>
+        <v>330</v>
       </c>
       <c r="J59" s="23" t="n">
-        <v>368.49</v>
+        <v>370.94</v>
       </c>
       <c r="K59" s="24" t="n">
-        <v>351.51</v>
+        <v>332.85</v>
       </c>
       <c r="L59" s="23" t="n">
-        <v>333.6</v>
+        <v>326.84</v>
       </c>
       <c r="M59" s="24" t="n">
-        <v>354.73</v>
+        <v>333.7</v>
       </c>
     </row>
     <row r="60">
@@ -9367,25 +9367,25 @@
         <v>334.39</v>
       </c>
       <c r="G60" s="23" t="n">
-        <v>357.5</v>
+        <v>347.27</v>
       </c>
       <c r="H60" s="24" t="n">
-        <v>356.33</v>
+        <v>355.53</v>
       </c>
       <c r="I60" s="23" t="n">
-        <v>351.52</v>
+        <v>336.91</v>
       </c>
       <c r="J60" s="23" t="n">
-        <v>368.49</v>
+        <v>371.45</v>
       </c>
       <c r="K60" s="24" t="n">
-        <v>353.8</v>
+        <v>341.88</v>
       </c>
       <c r="L60" s="23" t="n">
-        <v>351.53</v>
+        <v>338.51</v>
       </c>
       <c r="M60" s="24" t="n">
-        <v>363.67</v>
+        <v>340.69</v>
       </c>
     </row>
     <row r="61">
@@ -9408,25 +9408,25 @@
         <v>334.39</v>
       </c>
       <c r="G61" s="23" t="n">
-        <v>366.76</v>
+        <v>356.32</v>
       </c>
       <c r="H61" s="24" t="n">
-        <v>363.21</v>
+        <v>362.39</v>
       </c>
       <c r="I61" s="23" t="n">
-        <v>374.18</v>
+        <v>357.25</v>
       </c>
       <c r="J61" s="23" t="n">
-        <v>368.03</v>
+        <v>373.39</v>
       </c>
       <c r="K61" s="24" t="n">
-        <v>359.79</v>
+        <v>347.66</v>
       </c>
       <c r="L61" s="23" t="n">
-        <v>362.47</v>
+        <v>345.56</v>
       </c>
       <c r="M61" s="24" t="n">
-        <v>372.42</v>
+        <v>352.3</v>
       </c>
     </row>
     <row r="62">
@@ -9449,25 +9449,25 @@
         <v>410</v>
       </c>
       <c r="G62" s="23" t="n">
-        <v>365.85</v>
+        <v>353.42</v>
       </c>
       <c r="H62" s="24" t="n">
-        <v>373.02</v>
+        <v>372</v>
       </c>
       <c r="I62" s="23" t="n">
-        <v>369.76</v>
+        <v>329.19</v>
       </c>
       <c r="J62" s="23" t="n">
-        <v>367.32</v>
+        <v>369.31</v>
       </c>
       <c r="K62" s="24" t="n">
-        <v>362.03</v>
+        <v>356.98</v>
       </c>
       <c r="L62" s="23" t="n">
-        <v>357.3</v>
+        <v>342.92</v>
       </c>
       <c r="M62" s="24" t="n">
-        <v>366.29</v>
+        <v>352.63</v>
       </c>
     </row>
     <row r="63">
@@ -9490,25 +9490,25 @@
         <v>410</v>
       </c>
       <c r="G63" s="23" t="n">
-        <v>366.36</v>
+        <v>359.85</v>
       </c>
       <c r="H63" s="24" t="n">
-        <v>373.1</v>
+        <v>372.16</v>
       </c>
       <c r="I63" s="23" t="n">
-        <v>371.57</v>
+        <v>349.79</v>
       </c>
       <c r="J63" s="23" t="n">
-        <v>366.24</v>
+        <v>369.16</v>
       </c>
       <c r="K63" s="24" t="n">
-        <v>361.85</v>
+        <v>359.51</v>
       </c>
       <c r="L63" s="23" t="n">
-        <v>361.08</v>
+        <v>353.11</v>
       </c>
       <c r="M63" s="24" t="n">
-        <v>364.79</v>
+        <v>356.77</v>
       </c>
     </row>
     <row r="64">
@@ -9531,25 +9531,25 @@
         <v>410</v>
       </c>
       <c r="G64" s="23" t="n">
-        <v>378.05</v>
+        <v>376.82</v>
       </c>
       <c r="H64" s="24" t="n">
-        <v>387.9</v>
+        <v>386.82</v>
       </c>
       <c r="I64" s="23" t="n">
-        <v>380.24</v>
+        <v>372.01</v>
       </c>
       <c r="J64" s="23" t="n">
-        <v>371.28</v>
+        <v>374.95</v>
       </c>
       <c r="K64" s="24" t="n">
-        <v>375.76</v>
+        <v>370.97</v>
       </c>
       <c r="L64" s="23" t="n">
-        <v>370.09</v>
+        <v>376.79</v>
       </c>
       <c r="M64" s="24" t="n">
-        <v>383.62</v>
+        <v>380.05</v>
       </c>
     </row>
     <row r="65">
@@ -9572,25 +9572,25 @@
         <v>410</v>
       </c>
       <c r="G65" s="23" t="n">
-        <v>394.75</v>
+        <v>395.26</v>
       </c>
       <c r="H65" s="24" t="n">
-        <v>405.14</v>
+        <v>403.86</v>
       </c>
       <c r="I65" s="23" t="n">
-        <v>397.64</v>
+        <v>402.4</v>
       </c>
       <c r="J65" s="23" t="n">
-        <v>389.21</v>
+        <v>391.08</v>
       </c>
       <c r="K65" s="24" t="n">
-        <v>388.13</v>
+        <v>385.99</v>
       </c>
       <c r="L65" s="23" t="n">
-        <v>389.53</v>
+        <v>391.46</v>
       </c>
       <c r="M65" s="24" t="n">
-        <v>399.53</v>
+        <v>396.84</v>
       </c>
     </row>
     <row r="66">
@@ -9613,25 +9613,25 @@
         <v>439</v>
       </c>
       <c r="G66" s="23" t="n">
-        <v>403.84</v>
+        <v>403.54</v>
       </c>
       <c r="H66" s="24" t="n">
-        <v>397.9</v>
+        <v>396.49</v>
       </c>
       <c r="I66" s="23" t="n">
-        <v>411.22</v>
+        <v>403.43</v>
       </c>
       <c r="J66" s="23" t="n">
-        <v>401.49</v>
+        <v>407.01</v>
       </c>
       <c r="K66" s="24" t="n">
-        <v>399.1</v>
+        <v>400.22</v>
       </c>
       <c r="L66" s="23" t="n">
-        <v>404.72</v>
+        <v>407.82</v>
       </c>
       <c r="M66" s="24" t="n">
-        <v>407.83</v>
+        <v>405.76</v>
       </c>
     </row>
     <row r="67">
@@ -9654,25 +9654,25 @@
         <v>439</v>
       </c>
       <c r="G67" s="23" t="n">
-        <v>411.62</v>
+        <v>411.07</v>
       </c>
       <c r="H67" s="24" t="n">
-        <v>405.58</v>
+        <v>404.33</v>
       </c>
       <c r="I67" s="23" t="n">
-        <v>420.19</v>
+        <v>413.96</v>
       </c>
       <c r="J67" s="23" t="n">
-        <v>407.85</v>
+        <v>413.74</v>
       </c>
       <c r="K67" s="24" t="n">
-        <v>403.29</v>
+        <v>403.76</v>
       </c>
       <c r="L67" s="23" t="n">
-        <v>417.11</v>
+        <v>416.6</v>
       </c>
       <c r="M67" s="24" t="n">
-        <v>414.83</v>
+        <v>413.33</v>
       </c>
     </row>
     <row r="68">
@@ -9695,25 +9695,25 @@
         <v>439</v>
       </c>
       <c r="G68" s="23" t="n">
-        <v>414.49</v>
+        <v>414.18</v>
       </c>
       <c r="H68" s="24" t="n">
-        <v>414.56</v>
+        <v>413.45</v>
       </c>
       <c r="I68" s="23" t="n">
-        <v>419.38</v>
+        <v>419.52</v>
       </c>
       <c r="J68" s="23" t="n">
-        <v>411.6</v>
+        <v>414.99</v>
       </c>
       <c r="K68" s="24" t="n">
-        <v>404.52</v>
+        <v>400.5</v>
       </c>
       <c r="L68" s="23" t="n">
-        <v>419.82</v>
+        <v>420.83</v>
       </c>
       <c r="M68" s="24" t="n">
-        <v>416.84</v>
+        <v>415.28</v>
       </c>
     </row>
     <row r="69">
@@ -9736,25 +9736,25 @@
         <v>439</v>
       </c>
       <c r="G69" s="23" t="n">
-        <v>413.64</v>
+        <v>411.22</v>
       </c>
       <c r="H69" s="24" t="n">
-        <v>421.22</v>
+        <v>420.29</v>
       </c>
       <c r="I69" s="23" t="n">
-        <v>422.36</v>
+        <v>412.24</v>
       </c>
       <c r="J69" s="23" t="n">
-        <v>411</v>
+        <v>415.34</v>
       </c>
       <c r="K69" s="24" t="n">
-        <v>404.59</v>
+        <v>400.62</v>
       </c>
       <c r="L69" s="23" t="n">
-        <v>414.19</v>
+        <v>414.57</v>
       </c>
       <c r="M69" s="24" t="n">
-        <v>408.85</v>
+        <v>404.68</v>
       </c>
     </row>
     <row r="70">
@@ -9777,25 +9777,25 @@
         <v>429.01</v>
       </c>
       <c r="G70" s="23" t="n">
-        <v>411.33</v>
+        <v>408.5</v>
       </c>
       <c r="H70" s="24" t="n">
-        <v>419.37</v>
+        <v>418.69</v>
       </c>
       <c r="I70" s="23" t="n">
-        <v>411.79</v>
+        <v>405.57</v>
       </c>
       <c r="J70" s="23" t="n">
-        <v>412.49</v>
+        <v>413.91</v>
       </c>
       <c r="K70" s="24" t="n">
-        <v>404.39</v>
+        <v>398.83</v>
       </c>
       <c r="L70" s="23" t="n">
-        <v>414.3</v>
+        <v>413.33</v>
       </c>
       <c r="M70" s="24" t="n">
-        <v>406.36</v>
+        <v>401.34</v>
       </c>
     </row>
     <row r="71">
@@ -9818,25 +9818,25 @@
         <v>429.01</v>
       </c>
       <c r="G71" s="23" t="n">
-        <v>413.22</v>
+        <v>409.04</v>
       </c>
       <c r="H71" s="24" t="n">
-        <v>425.86</v>
+        <v>425.14</v>
       </c>
       <c r="I71" s="23" t="n">
-        <v>414</v>
+        <v>411.49</v>
       </c>
       <c r="J71" s="23" t="n">
-        <v>413.58</v>
+        <v>414.53</v>
       </c>
       <c r="K71" s="24" t="n">
-        <v>406.58</v>
+        <v>400.6</v>
       </c>
       <c r="L71" s="23" t="n">
-        <v>415.98</v>
+        <v>405.35</v>
       </c>
       <c r="M71" s="24" t="n">
-        <v>404.42</v>
+        <v>398.16</v>
       </c>
     </row>
     <row r="72">
@@ -9859,25 +9859,25 @@
         <v>429.01</v>
       </c>
       <c r="G72" s="23" t="n">
-        <v>413.39</v>
+        <v>412.94</v>
       </c>
       <c r="H72" s="24" t="n">
-        <v>425.76</v>
+        <v>425.06</v>
       </c>
       <c r="I72" s="23" t="n">
-        <v>409.09</v>
+        <v>421.62</v>
       </c>
       <c r="J72" s="23" t="n">
-        <v>413.33</v>
+        <v>414.53</v>
       </c>
       <c r="K72" s="24" t="n">
-        <v>406.44</v>
+        <v>400</v>
       </c>
       <c r="L72" s="23" t="n">
-        <v>419.87</v>
+        <v>415.46</v>
       </c>
       <c r="M72" s="24" t="n">
-        <v>407.01</v>
+        <v>401.3</v>
       </c>
     </row>
     <row r="73">
@@ -9900,25 +9900,25 @@
         <v>429.01</v>
       </c>
       <c r="G73" s="23" t="n">
-        <v>400.54</v>
+        <v>399.67</v>
       </c>
       <c r="H73" s="24" t="n">
-        <v>416.8</v>
+        <v>416.34</v>
       </c>
       <c r="I73" s="23" t="n">
-        <v>405.61</v>
+        <v>406.52</v>
       </c>
       <c r="J73" s="23" t="n">
-        <v>388.72</v>
+        <v>391.88</v>
       </c>
       <c r="K73" s="24" t="n">
-        <v>399.66</v>
+        <v>392.88</v>
       </c>
       <c r="L73" s="23" t="n">
-        <v>402.3</v>
+        <v>404.08</v>
       </c>
       <c r="M73" s="24" t="n">
-        <v>391.13</v>
+        <v>386.94</v>
       </c>
     </row>
     <row r="74">
@@ -9941,25 +9941,25 @@
         <v>375.01</v>
       </c>
       <c r="G74" s="23" t="n">
-        <v>390.88</v>
+        <v>388.34</v>
       </c>
       <c r="H74" s="24" t="n">
-        <v>404.37</v>
+        <v>403.88</v>
       </c>
       <c r="I74" s="23" t="n">
-        <v>391.49</v>
+        <v>397.22</v>
       </c>
       <c r="J74" s="23" t="n">
-        <v>380.52</v>
+        <v>383.76</v>
       </c>
       <c r="K74" s="24" t="n">
-        <v>389.49</v>
+        <v>381.13</v>
       </c>
       <c r="L74" s="23" t="n">
-        <v>396.52</v>
+        <v>387.85</v>
       </c>
       <c r="M74" s="24" t="n">
-        <v>383.71</v>
+        <v>376.78</v>
       </c>
     </row>
     <row r="75">
@@ -9982,25 +9982,25 @@
         <v>375.01</v>
       </c>
       <c r="G75" s="23" t="n">
-        <v>385.7</v>
+        <v>382.18</v>
       </c>
       <c r="H75" s="24" t="n">
-        <v>393.54</v>
+        <v>392.97</v>
       </c>
       <c r="I75" s="23" t="n">
-        <v>391.7</v>
+        <v>392.28</v>
       </c>
       <c r="J75" s="23" t="n">
-        <v>380.14</v>
+        <v>379.09</v>
       </c>
       <c r="K75" s="24" t="n">
-        <v>384.51</v>
+        <v>376.45</v>
       </c>
       <c r="L75" s="23" t="n">
-        <v>387.68</v>
+        <v>381.29</v>
       </c>
       <c r="M75" s="24" t="n">
-        <v>377.03</v>
+        <v>371.3</v>
       </c>
     </row>
     <row r="76">
@@ -10023,25 +10023,25 @@
         <v>375.01</v>
       </c>
       <c r="G76" s="23" t="n">
-        <v>374.78</v>
+        <v>371.87</v>
       </c>
       <c r="H76" s="24" t="n">
-        <v>377.83</v>
+        <v>377.36</v>
       </c>
       <c r="I76" s="23" t="n">
-        <v>379.25</v>
+        <v>382.01</v>
       </c>
       <c r="J76" s="23" t="n">
-        <v>368.84</v>
+        <v>371.23</v>
       </c>
       <c r="K76" s="24" t="n">
-        <v>380.28</v>
+        <v>371.7</v>
       </c>
       <c r="L76" s="23" t="n">
-        <v>373.94</v>
+        <v>366.88</v>
       </c>
       <c r="M76" s="24" t="n">
-        <v>368.55</v>
+        <v>362.15</v>
       </c>
     </row>
     <row r="77">
@@ -10064,25 +10064,25 @@
         <v>375.01</v>
       </c>
       <c r="G77" s="23" t="n">
-        <v>368.63</v>
+        <v>364.33</v>
       </c>
       <c r="H77" s="24" t="n">
-        <v>360.76</v>
+        <v>360.34</v>
       </c>
       <c r="I77" s="23" t="n">
-        <v>373.44</v>
+        <v>370.18</v>
       </c>
       <c r="J77" s="23" t="n">
-        <v>366.12</v>
+        <v>366.33</v>
       </c>
       <c r="K77" s="24" t="n">
-        <v>377.97</v>
+        <v>368.39</v>
       </c>
       <c r="L77" s="23" t="n">
-        <v>368.3</v>
+        <v>362.51</v>
       </c>
       <c r="M77" s="24" t="n">
-        <v>364.36</v>
+        <v>357.97</v>
       </c>
     </row>
     <row r="78">
@@ -10105,25 +10105,25 @@
         <v>338.22</v>
       </c>
       <c r="G78" s="23" t="n">
-        <v>347.11</v>
+        <v>337.69</v>
       </c>
       <c r="H78" s="24" t="n">
-        <v>334.42</v>
+        <v>334.25</v>
       </c>
       <c r="I78" s="23" t="n">
-        <v>349.95</v>
+        <v>319.24</v>
       </c>
       <c r="J78" s="23" t="n">
-        <v>364.66</v>
+        <v>364.84</v>
       </c>
       <c r="K78" s="24" t="n">
-        <v>358.77</v>
+        <v>346.52</v>
       </c>
       <c r="L78" s="23" t="n">
-        <v>335.29</v>
+        <v>330.52</v>
       </c>
       <c r="M78" s="24" t="n">
-        <v>339.03</v>
+        <v>331.92</v>
       </c>
     </row>
     <row r="79">
@@ -10146,25 +10146,25 @@
         <v>338.22</v>
       </c>
       <c r="G79" s="23" t="n">
-        <v>334.1</v>
+        <v>328.86</v>
       </c>
       <c r="H79" s="24" t="n">
-        <v>319.39</v>
+        <v>319.27</v>
       </c>
       <c r="I79" s="23" t="n">
-        <v>334.71</v>
+        <v>324.64</v>
       </c>
       <c r="J79" s="23" t="n">
-        <v>351.16</v>
+        <v>350.76</v>
       </c>
       <c r="K79" s="24" t="n">
-        <v>349.7</v>
+        <v>327.79</v>
       </c>
       <c r="L79" s="23" t="n">
-        <v>323.55</v>
+        <v>324.28</v>
       </c>
       <c r="M79" s="24" t="n">
-        <v>325.42</v>
+        <v>326.38</v>
       </c>
     </row>
     <row r="80">
@@ -10187,25 +10187,25 @@
         <v>338.22</v>
       </c>
       <c r="G80" s="23" t="n">
-        <v>315.28</v>
+        <v>305.14</v>
       </c>
       <c r="H80" s="24" t="n">
-        <v>305.26</v>
+        <v>305.4</v>
       </c>
       <c r="I80" s="23" t="n">
-        <v>326.43</v>
+        <v>314.37</v>
       </c>
       <c r="J80" s="23" t="n">
-        <v>310.61</v>
+        <v>319.74</v>
       </c>
       <c r="K80" s="24" t="n">
-        <v>328.51</v>
+        <v>309.89</v>
       </c>
       <c r="L80" s="23" t="n">
-        <v>311.53</v>
+        <v>297.1</v>
       </c>
       <c r="M80" s="24" t="n">
-        <v>308.11</v>
+        <v>284.61</v>
       </c>
     </row>
     <row r="81">
@@ -10228,25 +10228,25 @@
         <v>338.22</v>
       </c>
       <c r="G81" s="23" t="n">
-        <v>283.65</v>
+        <v>271.61</v>
       </c>
       <c r="H81" s="24" t="n">
-        <v>295.89</v>
+        <v>296.05</v>
       </c>
       <c r="I81" s="23" t="n">
-        <v>291.24</v>
+        <v>269.45</v>
       </c>
       <c r="J81" s="23" t="n">
-        <v>260.09</v>
+        <v>270.94</v>
       </c>
       <c r="K81" s="24" t="n">
-        <v>308.07</v>
+        <v>284.04</v>
       </c>
       <c r="L81" s="23" t="n">
-        <v>275.06</v>
+        <v>259.2</v>
       </c>
       <c r="M81" s="24" t="n">
-        <v>271.83</v>
+        <v>252.11</v>
       </c>
     </row>
     <row r="82">
@@ -10269,25 +10269,25 @@
         <v>330</v>
       </c>
       <c r="G82" s="23" t="n">
-        <v>272.84</v>
+        <v>247.65</v>
       </c>
       <c r="H82" s="24" t="n">
-        <v>287.03</v>
+        <v>287.3</v>
       </c>
       <c r="I82" s="23" t="n">
-        <v>289.85</v>
+        <v>249.11</v>
       </c>
       <c r="J82" s="23" t="n">
-        <v>234.63</v>
+        <v>242.32</v>
       </c>
       <c r="K82" s="24" t="n">
-        <v>292.92</v>
+        <v>260.88</v>
       </c>
       <c r="L82" s="23" t="n">
-        <v>261.36</v>
+        <v>223.48</v>
       </c>
       <c r="M82" s="24" t="n">
-        <v>271.01</v>
+        <v>225.87</v>
       </c>
     </row>
     <row r="83">
@@ -10310,25 +10310,25 @@
         <v>330</v>
       </c>
       <c r="G83" s="23" t="n">
-        <v>306.44</v>
+        <v>277.03</v>
       </c>
       <c r="H83" s="24" t="n">
-        <v>292.88</v>
+        <v>293.01</v>
       </c>
       <c r="I83" s="23" t="n">
-        <v>323.46</v>
+        <v>279.63</v>
       </c>
       <c r="J83" s="23" t="n">
-        <v>315.76</v>
+        <v>306.23</v>
       </c>
       <c r="K83" s="24" t="n">
-        <v>321.21</v>
+        <v>283.51</v>
       </c>
       <c r="L83" s="23" t="n">
-        <v>277.88</v>
+        <v>253.96</v>
       </c>
       <c r="M83" s="24" t="n">
-        <v>306.3</v>
+        <v>247.88</v>
       </c>
     </row>
     <row r="84">
@@ -10351,25 +10351,25 @@
         <v>330</v>
       </c>
       <c r="G84" s="23" t="n">
-        <v>311.62</v>
+        <v>293.78</v>
       </c>
       <c r="H84" s="24" t="n">
-        <v>295.25</v>
+        <v>295.23</v>
       </c>
       <c r="I84" s="23" t="n">
-        <v>324.25</v>
+        <v>298.02</v>
       </c>
       <c r="J84" s="23" t="n">
-        <v>318.41</v>
+        <v>321.09</v>
       </c>
       <c r="K84" s="24" t="n">
-        <v>320.78</v>
+        <v>290.61</v>
       </c>
       <c r="L84" s="23" t="n">
-        <v>297.6</v>
+        <v>285.16</v>
       </c>
       <c r="M84" s="24" t="n">
-        <v>311.99</v>
+        <v>273.19</v>
       </c>
     </row>
     <row r="85">
@@ -10392,25 +10392,25 @@
         <v>330</v>
       </c>
       <c r="G85" s="23" t="n">
-        <v>328.66</v>
+        <v>323.27</v>
       </c>
       <c r="H85" s="24" t="n">
-        <v>300.36</v>
+        <v>300.13</v>
       </c>
       <c r="I85" s="23" t="n">
-        <v>337.06</v>
+        <v>334.34</v>
       </c>
       <c r="J85" s="23" t="n">
-        <v>337.28</v>
+        <v>339.08</v>
       </c>
       <c r="K85" s="24" t="n">
-        <v>336.4</v>
+        <v>320.79</v>
       </c>
       <c r="L85" s="23" t="n">
-        <v>334.73</v>
+        <v>327.86</v>
       </c>
       <c r="M85" s="24" t="n">
-        <v>323.8</v>
+        <v>315.79</v>
       </c>
     </row>
     <row r="86">
@@ -10433,25 +10433,25 @@
         <v>330</v>
       </c>
       <c r="G86" s="23" t="n">
-        <v>340.1</v>
+        <v>336.6</v>
       </c>
       <c r="H86" s="24" t="n">
-        <v>305.61</v>
+        <v>305.07</v>
       </c>
       <c r="I86" s="23" t="n">
-        <v>344.73</v>
+        <v>349.89</v>
       </c>
       <c r="J86" s="23" t="n">
-        <v>352.1</v>
+        <v>350.56</v>
       </c>
       <c r="K86" s="24" t="n">
-        <v>344.65</v>
+        <v>331.58</v>
       </c>
       <c r="L86" s="23" t="n">
-        <v>348.66</v>
+        <v>339.13</v>
       </c>
       <c r="M86" s="24" t="n">
-        <v>342.09</v>
+        <v>341</v>
       </c>
     </row>
     <row r="87">
@@ -10474,25 +10474,25 @@
         <v>330</v>
       </c>
       <c r="G87" s="23" t="n">
-        <v>318.58</v>
+        <v>295.88</v>
       </c>
       <c r="H87" s="24" t="n">
-        <v>292.11</v>
+        <v>292.12</v>
       </c>
       <c r="I87" s="23" t="n">
-        <v>329.98</v>
+        <v>302.46</v>
       </c>
       <c r="J87" s="23" t="n">
-        <v>320.64</v>
+        <v>320.07</v>
       </c>
       <c r="K87" s="24" t="n">
-        <v>326.7</v>
+        <v>300.13</v>
       </c>
       <c r="L87" s="23" t="n">
-        <v>313.96</v>
+        <v>281.98</v>
       </c>
       <c r="M87" s="24" t="n">
-        <v>325.6</v>
+        <v>278.84</v>
       </c>
     </row>
     <row r="88">
@@ -10515,25 +10515,25 @@
         <v>330</v>
       </c>
       <c r="G88" s="23" t="n">
-        <v>306.4</v>
+        <v>267.91</v>
       </c>
       <c r="H88" s="24" t="n">
-        <v>285.01</v>
+        <v>285.11</v>
       </c>
       <c r="I88" s="23" t="n">
-        <v>318.26</v>
+        <v>271.98</v>
       </c>
       <c r="J88" s="23" t="n">
-        <v>312.93</v>
+        <v>289.47</v>
       </c>
       <c r="K88" s="24" t="n">
-        <v>310.89</v>
+        <v>278.52</v>
       </c>
       <c r="L88" s="23" t="n">
-        <v>291.79</v>
+        <v>239.67</v>
       </c>
       <c r="M88" s="24" t="n">
-        <v>317.64</v>
+        <v>244.7</v>
       </c>
     </row>
     <row r="89">
@@ -10556,25 +10556,25 @@
         <v>330</v>
       </c>
       <c r="G89" s="23" t="n">
-        <v>303.65</v>
+        <v>262.53</v>
       </c>
       <c r="H89" s="24" t="n">
-        <v>277.18</v>
+        <v>277.22</v>
       </c>
       <c r="I89" s="23" t="n">
-        <v>315.04</v>
+        <v>262.79</v>
       </c>
       <c r="J89" s="23" t="n">
-        <v>304.61</v>
+        <v>282.63</v>
       </c>
       <c r="K89" s="24" t="n">
-        <v>304.34</v>
+        <v>274.23</v>
       </c>
       <c r="L89" s="23" t="n">
-        <v>295.28</v>
+        <v>245.22</v>
       </c>
       <c r="M89" s="24" t="n">
-        <v>322.9</v>
+        <v>234.96</v>
       </c>
     </row>
     <row r="90">
@@ -10597,25 +10597,25 @@
         <v>325</v>
       </c>
       <c r="G90" s="23" t="n">
-        <v>283.24</v>
+        <v>247.97</v>
       </c>
       <c r="H90" s="24" t="n">
-        <v>270.36</v>
+        <v>270.37</v>
       </c>
       <c r="I90" s="23" t="n">
-        <v>312.4</v>
+        <v>249.5</v>
       </c>
       <c r="J90" s="23" t="n">
-        <v>235.77</v>
+        <v>249.32</v>
       </c>
       <c r="K90" s="24" t="n">
-        <v>300.33</v>
+        <v>270.69</v>
       </c>
       <c r="L90" s="23" t="n">
-        <v>284.31</v>
+        <v>222.13</v>
       </c>
       <c r="M90" s="24" t="n">
-        <v>293.02</v>
+        <v>228.06</v>
       </c>
     </row>
     <row r="91">
@@ -10638,25 +10638,25 @@
         <v>325</v>
       </c>
       <c r="G91" s="23" t="n">
-        <v>312.13</v>
+        <v>271.63</v>
       </c>
       <c r="H91" s="24" t="n">
-        <v>282.05</v>
+        <v>281.9</v>
       </c>
       <c r="I91" s="23" t="n">
-        <v>323.13</v>
+        <v>268.32</v>
       </c>
       <c r="J91" s="23" t="n">
-        <v>311.41</v>
+        <v>300.76</v>
       </c>
       <c r="K91" s="24" t="n">
-        <v>308.86</v>
+        <v>285.39</v>
       </c>
       <c r="L91" s="23" t="n">
-        <v>304.63</v>
+        <v>251.89</v>
       </c>
       <c r="M91" s="24" t="n">
-        <v>339.77</v>
+        <v>243.47</v>
       </c>
     </row>
     <row r="92">
@@ -10679,25 +10679,25 @@
         <v>325</v>
       </c>
       <c r="G92" s="23" t="n">
-        <v>312.67</v>
+        <v>272.62</v>
       </c>
       <c r="H92" s="24" t="n">
-        <v>283.12</v>
+        <v>282.91</v>
       </c>
       <c r="I92" s="23" t="n">
-        <v>330.24</v>
+        <v>265.05</v>
       </c>
       <c r="J92" s="23" t="n">
-        <v>311.88</v>
+        <v>301.72</v>
       </c>
       <c r="K92" s="24" t="n">
-        <v>310.72</v>
+        <v>284.43</v>
       </c>
       <c r="L92" s="23" t="n">
-        <v>301.08</v>
+        <v>260.51</v>
       </c>
       <c r="M92" s="24" t="n">
-        <v>335.99</v>
+        <v>243.1</v>
       </c>
     </row>
     <row r="93">
@@ -10720,25 +10720,25 @@
         <v>325</v>
       </c>
       <c r="G93" s="23" t="n">
-        <v>323.93</v>
+        <v>290.32</v>
       </c>
       <c r="H93" s="24" t="n">
-        <v>289.1</v>
+        <v>288.65</v>
       </c>
       <c r="I93" s="23" t="n">
-        <v>346.93</v>
+        <v>284.97</v>
       </c>
       <c r="J93" s="23" t="n">
-        <v>332.82</v>
+        <v>321.49</v>
       </c>
       <c r="K93" s="24" t="n">
-        <v>325.53</v>
+        <v>296.78</v>
       </c>
       <c r="L93" s="23" t="n">
-        <v>312.95</v>
+        <v>281.71</v>
       </c>
       <c r="M93" s="24" t="n">
-        <v>333.01</v>
+        <v>269.33</v>
       </c>
     </row>
     <row r="94">
@@ -10761,25 +10761,25 @@
         <v>325</v>
       </c>
       <c r="G94" s="23" t="n">
-        <v>337.93</v>
+        <v>317.17</v>
       </c>
       <c r="H94" s="24" t="n">
-        <v>292.9</v>
+        <v>292.36</v>
       </c>
       <c r="I94" s="23" t="n">
-        <v>352.13</v>
+        <v>319.47</v>
       </c>
       <c r="J94" s="23" t="n">
-        <v>353.25</v>
+        <v>340.32</v>
       </c>
       <c r="K94" s="24" t="n">
-        <v>344.43</v>
+        <v>317.15</v>
       </c>
       <c r="L94" s="23" t="n">
-        <v>335.6</v>
+        <v>323.86</v>
       </c>
       <c r="M94" s="24" t="n">
-        <v>345.51</v>
+        <v>308.62</v>
       </c>
     </row>
     <row r="95">
@@ -10802,25 +10802,25 @@
         <v>325</v>
       </c>
       <c r="G95" s="23" t="n">
-        <v>297.65</v>
+        <v>258.25</v>
       </c>
       <c r="H95" s="24" t="n">
-        <v>280.12</v>
+        <v>280.01</v>
       </c>
       <c r="I95" s="23" t="n">
-        <v>295.43</v>
+        <v>254.28</v>
       </c>
       <c r="J95" s="23" t="n">
-        <v>312.35</v>
+        <v>297.9</v>
       </c>
       <c r="K95" s="24" t="n">
-        <v>313.44</v>
+        <v>267.04</v>
       </c>
       <c r="L95" s="23" t="n">
-        <v>274.24</v>
+        <v>237</v>
       </c>
       <c r="M95" s="24" t="n">
-        <v>309.31</v>
+        <v>216.23</v>
       </c>
     </row>
     <row r="96">
@@ -10843,25 +10843,25 @@
         <v>325</v>
       </c>
       <c r="G96" s="23" t="n">
-        <v>287.71</v>
+        <v>254.52</v>
       </c>
       <c r="H96" s="24" t="n">
-        <v>274.98</v>
+        <v>274.79</v>
       </c>
       <c r="I96" s="23" t="n">
-        <v>285.34</v>
+        <v>244.67</v>
       </c>
       <c r="J96" s="23" t="n">
-        <v>296.66</v>
+        <v>302.98</v>
       </c>
       <c r="K96" s="24" t="n">
-        <v>293.1</v>
+        <v>254.62</v>
       </c>
       <c r="L96" s="23" t="n">
-        <v>267</v>
+        <v>243.88</v>
       </c>
       <c r="M96" s="24" t="n">
-        <v>308.39</v>
+        <v>209.12</v>
       </c>
     </row>
     <row r="97">
@@ -10886,25 +10886,25 @@
         <v>325</v>
       </c>
       <c r="G97" s="23" t="n">
-        <v>289.1</v>
+        <v>253.91</v>
       </c>
       <c r="H97" s="24" t="n">
-        <v>274.33</v>
+        <v>273.94</v>
       </c>
       <c r="I97" s="23" t="n">
-        <v>280.35</v>
+        <v>245.59</v>
       </c>
       <c r="J97" s="23" t="n">
-        <v>307.49</v>
+        <v>289.16</v>
       </c>
       <c r="K97" s="24" t="n">
-        <v>291.7</v>
+        <v>255.87</v>
       </c>
       <c r="L97" s="23" t="n">
-        <v>271.21</v>
+        <v>243.29</v>
       </c>
       <c r="M97" s="24" t="n">
-        <v>308.98</v>
+        <v>218.2</v>
       </c>
     </row>
   </sheetData>
